--- a/research/traditional_assets/database/data/turkey/turkey_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_real_estate_development.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ibse_kuyas" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,37 +590,37 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0534</v>
+        <v>0.415</v>
       </c>
       <c r="E2">
-        <v>0.298</v>
+        <v>0.586</v>
       </c>
       <c r="G2">
-        <v>-0.4317596566523605</v>
+        <v>0.1494039735099338</v>
       </c>
       <c r="H2">
-        <v>-0.4317596566523605</v>
+        <v>0.1494039735099338</v>
       </c>
       <c r="I2">
-        <v>-0.4</v>
+        <v>0.192317880794702</v>
       </c>
       <c r="J2">
-        <v>-0.3311072261072261</v>
+        <v>0.1583590477895114</v>
       </c>
       <c r="K2">
-        <v>1.713</v>
+        <v>11.04</v>
       </c>
       <c r="L2">
-        <v>0.7351931330472103</v>
+        <v>1.462251655629139</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.00388785046728972</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.09420289855072465</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -630,76 +632,79 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.04</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>2.505</v>
+        <v>2.23</v>
       </c>
       <c r="V2">
-        <v>0.0232159406858202</v>
+        <v>0.008336448598130842</v>
       </c>
       <c r="W2">
-        <v>0.05926878306878307</v>
+        <v>0.2864161249146555</v>
       </c>
       <c r="X2">
-        <v>0.06956590661331756</v>
+        <v>0.1267596365271132</v>
       </c>
       <c r="Y2">
-        <v>-0.01029712354453449</v>
+        <v>0.1596564883875423</v>
       </c>
       <c r="Z2">
-        <v>0.06382162813629891</v>
+        <v>0.1655810689299735</v>
       </c>
       <c r="AA2">
-        <v>-0.02081979078394022</v>
+        <v>0.01794070427201231</v>
       </c>
       <c r="AB2">
-        <v>0.0678221788543657</v>
+        <v>0.1263677675999581</v>
       </c>
       <c r="AC2">
-        <v>-0.08864196963830591</v>
+        <v>-0.1084270633279458</v>
       </c>
       <c r="AD2">
-        <v>11.302</v>
+        <v>4.708</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11.302</v>
+        <v>4.708</v>
       </c>
       <c r="AG2">
-        <v>8.797000000000001</v>
+        <v>2.478</v>
       </c>
       <c r="AH2">
-        <v>0.09481384540527844</v>
+        <v>0.01729559748427673</v>
       </c>
       <c r="AI2">
-        <v>0.2349590453619393</v>
+        <v>0.1542696113768923</v>
       </c>
       <c r="AJ2">
-        <v>0.07538325749590821</v>
+        <v>0.009178525657646179</v>
       </c>
       <c r="AK2">
-        <v>0.1929293593876791</v>
+        <v>0.08759898190045248</v>
       </c>
       <c r="AL2">
-        <v>0.002</v>
+        <v>0.226</v>
       </c>
       <c r="AM2">
-        <v>-2.11</v>
+        <v>-8.622999999999999</v>
       </c>
       <c r="AN2">
-        <v>-12.11361200428725</v>
+        <v>3.095332018408942</v>
       </c>
       <c r="AO2">
-        <v>-465.9999999999999</v>
+        <v>6.424778761061947</v>
       </c>
       <c r="AP2">
-        <v>-9.428724544480172</v>
+        <v>1.629191321499014</v>
       </c>
       <c r="AQ2">
-        <v>0.4417061611374407</v>
+        <v>-0.1683868723182187</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +715,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Türker Proje Gayrimenkul ve Yatirim Gelistirme A.S. (IBSE:TURGG)</t>
+          <t>Kuyumcukent Gayrimenkul Yatirimlari A.S. (IBSE:KUYAS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,20 +723,35 @@
           <t>Real Estate (Development)</t>
         </is>
       </c>
-      <c r="E3">
-        <v>0.223</v>
+      <c r="D3">
+        <v>0.415</v>
+      </c>
+      <c r="G3">
+        <v>0.1708609271523179</v>
+      </c>
+      <c r="H3">
+        <v>0.1708609271523179</v>
+      </c>
+      <c r="I3">
+        <v>0.2185430463576159</v>
+      </c>
+      <c r="J3">
+        <v>0.1850724897082513</v>
       </c>
       <c r="K3">
-        <v>0.6830000000000001</v>
+        <v>9.43</v>
+      </c>
+      <c r="L3">
+        <v>1.249006622516556</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.00736543909348442</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.1102863202545069</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -743,76 +763,79 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.04</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="V3">
-        <v>0.02528901734104046</v>
+        <v>0.01005665722379603</v>
       </c>
       <c r="W3">
-        <v>0.03613756613756614</v>
+        <v>0.4786802030456853</v>
       </c>
       <c r="X3">
-        <v>0.06387041883557819</v>
+        <v>0.1278704456757748</v>
       </c>
       <c r="Y3">
-        <v>-0.02773285269801205</v>
+        <v>0.3508097573699105</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.2496280376921805</v>
       </c>
       <c r="AA3">
-        <v>-0.0109064187375309</v>
+        <v>0.04619928243667704</v>
       </c>
       <c r="AB3">
-        <v>0.06387030208383837</v>
+        <v>0.1270881053085068</v>
       </c>
       <c r="AC3">
-        <v>-0.07477672082136927</v>
+        <v>-0.08088882287182975</v>
       </c>
       <c r="AD3">
-        <v>0.002</v>
+        <v>4.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.002</v>
+        <v>4.7</v>
       </c>
       <c r="AG3">
-        <v>-1.748</v>
+        <v>3.28</v>
       </c>
       <c r="AH3">
-        <v>2.890089881795324e-05</v>
+        <v>0.03221384509938315</v>
       </c>
       <c r="AI3">
-        <v>0.0001169453865045024</v>
+        <v>0.2270531400966184</v>
       </c>
       <c r="AJ3">
-        <v>-0.02591472454486153</v>
+        <v>0.02270210409745294</v>
       </c>
       <c r="AK3">
-        <v>-0.1138613861386139</v>
+        <v>0.1701244813278008</v>
       </c>
       <c r="AL3">
-        <v>0.002</v>
+        <v>0.224</v>
       </c>
       <c r="AM3">
-        <v>-0.29</v>
+        <v>-8.465999999999999</v>
       </c>
       <c r="AN3">
-        <v>-0.008620689655172414</v>
+        <v>2.732558139534884</v>
       </c>
       <c r="AO3">
-        <v>-116</v>
+        <v>7.366071428571428</v>
       </c>
       <c r="AP3">
-        <v>7.53448275862069</v>
+        <v>1.906976744186047</v>
       </c>
       <c r="AQ3">
-        <v>0.8</v>
+        <v>-0.1948972360028349</v>
       </c>
     </row>
     <row r="4">
@@ -823,7 +846,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kuyumcukent Gayrimenkul Yatirimlari A.S. (IBSE:KUYAS)</t>
+          <t>Türker Proje Gayrimenkul ve Yatirim Gelistirme A.S. (IBSE:TURGG)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -831,29 +854,11 @@
           <t>Real Estate (Development)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.0534</v>
-      </c>
       <c r="E4">
-        <v>0.373</v>
-      </c>
-      <c r="G4">
-        <v>-0.3188841201716738</v>
-      </c>
-      <c r="H4">
-        <v>-0.3188841201716738</v>
-      </c>
-      <c r="I4">
-        <v>-0.3004291845493562</v>
-      </c>
-      <c r="J4">
-        <v>-0.2578683834048641</v>
+        <v>0.586</v>
       </c>
       <c r="K4">
-        <v>1.03</v>
-      </c>
-      <c r="L4">
-        <v>0.4420600858369099</v>
+        <v>1.61</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,70 +882,8785 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.755</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="V4">
-        <v>0.01950904392764858</v>
+        <v>0.006413301662707839</v>
       </c>
       <c r="W4">
-        <v>0.0824</v>
+        <v>0.09415204678362572</v>
       </c>
       <c r="X4">
-        <v>0.07526139439105693</v>
+        <v>0.1256488273784517</v>
       </c>
       <c r="Y4">
-        <v>0.007138605608943069</v>
+        <v>-0.03149678059482595</v>
       </c>
       <c r="Z4">
-        <v>0.1191815856777494</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.03073316283034953</v>
+        <v>-0.01031787389265242</v>
       </c>
       <c r="AB4">
-        <v>0.07177405562489302</v>
+        <v>0.1256474298914094</v>
       </c>
       <c r="AC4">
-        <v>-0.1025072184552425</v>
+        <v>-0.1359653037840618</v>
       </c>
       <c r="AD4">
-        <v>11.3</v>
+        <v>0.008</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>11.3</v>
+        <v>0.008</v>
       </c>
       <c r="AG4">
-        <v>10.545</v>
+        <v>-0.802</v>
       </c>
       <c r="AH4">
-        <v>0.226</v>
+        <v>6.333723912974634e-05</v>
       </c>
       <c r="AI4">
-        <v>0.3645161290322581</v>
+        <v>0.0008148299042574863</v>
       </c>
       <c r="AJ4">
-        <v>0.2141334145598538</v>
+        <v>-0.00639054008828826</v>
       </c>
       <c r="AK4">
-        <v>0.3486526698627873</v>
+        <v>-0.08903197158081705</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AM4">
-        <v>-1.82</v>
+        <v>-0.157</v>
       </c>
       <c r="AN4">
-        <v>-16.11982881597718</v>
+        <v>-0.04020100502512563</v>
+      </c>
+      <c r="AO4">
+        <v>-99</v>
       </c>
       <c r="AP4">
-        <v>-15.04279600570614</v>
+        <v>4.030150753768845</v>
       </c>
       <c r="AQ4">
-        <v>0.3846153846153846</v>
+        <v>1.261146496815287</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Kuyumcukent Gayrimenkul Yatirimlari A.S. (IBSE:KUYAS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IBSE:KUYAS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Real Estate (Development)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0322138450993831</v>
+      </c>
+      <c r="F2">
+        <v>0.04</v>
+      </c>
+      <c r="G2">
+        <v>141.2</v>
+      </c>
+      <c r="H2">
+        <v>143.585130967099</v>
+      </c>
+      <c r="I2">
+        <v>144.48</v>
+      </c>
+      <c r="J2">
+        <v>148.001130967099</v>
+      </c>
+      <c r="K2">
+        <v>4.7</v>
+      </c>
+      <c r="L2">
+        <v>5.836</v>
+      </c>
+      <c r="M2">
+        <v>0.127088105308507</v>
+      </c>
+      <c r="N2">
+        <v>0.124987621483844</v>
+      </c>
+      <c r="O2">
+        <v>0.103584603211009</v>
+      </c>
+      <c r="P2">
+        <v>0.04235</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.127870445675775</v>
+      </c>
+      <c r="T2">
+        <v>0.128430855712337</v>
+      </c>
+      <c r="U2">
+        <v>0.519897856834613</v>
+      </c>
+      <c r="V2">
+        <v>0.52316893036239</v>
+      </c>
+      <c r="W2">
+        <v>5.140507196710075</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>141.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.1713229714353474</v>
+      </c>
+      <c r="AC2">
+        <v>0.1345254587155963</v>
+      </c>
+      <c r="AD2">
+        <v>0.23</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1.72</v>
+      </c>
+      <c r="AH2">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="AI2">
+        <v>2.492</v>
+      </c>
+      <c r="AJ2">
+        <v>4.7</v>
+      </c>
+      <c r="AK2">
+        <v>4.7</v>
+      </c>
+      <c r="AL2">
+        <v>0.224</v>
+      </c>
+      <c r="AM2">
+        <v>4.7</v>
+      </c>
+      <c r="AN2">
+        <v>1.42</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1256445917277387</v>
+      </c>
+      <c r="C2">
+        <v>148.3015179068745</v>
+      </c>
+      <c r="D2">
+        <v>146.8815179068745</v>
+      </c>
+      <c r="E2">
+        <v>-4.7</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.42</v>
+      </c>
+      <c r="H2">
+        <v>141.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1.72</v>
+      </c>
+      <c r="K2">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L2">
+        <v>1.65</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.65</v>
+      </c>
+      <c r="O2">
+        <v>0.3794999999999999</v>
+      </c>
+      <c r="P2">
+        <v>1.2705</v>
+      </c>
+      <c r="Q2">
+        <v>1.3405</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1256445917277387</v>
+      </c>
+      <c r="T2">
+        <v>0.5069057056397804</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.23</v>
+      </c>
+      <c r="W2">
+        <v>0.035189</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1254087391667649</v>
+      </c>
+      <c r="C3">
+        <v>147.2425050501043</v>
+      </c>
+      <c r="D3">
+        <v>147.2815050501044</v>
+      </c>
+      <c r="E3">
+        <v>-3.241000000000001</v>
+      </c>
+      <c r="F3">
+        <v>1.459</v>
+      </c>
+      <c r="G3">
+        <v>1.42</v>
+      </c>
+      <c r="H3">
+        <v>141.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1.72</v>
+      </c>
+      <c r="K3">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L3">
+        <v>1.65</v>
+      </c>
+      <c r="M3">
+        <v>0.06667629999999999</v>
+      </c>
+      <c r="N3">
+        <v>1.5833237</v>
+      </c>
+      <c r="O3">
+        <v>0.3641644509999999</v>
+      </c>
+      <c r="P3">
+        <v>1.219159249</v>
+      </c>
+      <c r="Q3">
+        <v>1.289159249</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1263200496633989</v>
+      </c>
+      <c r="T3">
+        <v>0.5108483055725344</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.23</v>
+      </c>
+      <c r="W3">
+        <v>0.035189</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>24.74642414171153</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1251975266057911</v>
+      </c>
+      <c r="C4">
+        <v>146.1435582262519</v>
+      </c>
+      <c r="D4">
+        <v>147.6415582262519</v>
+      </c>
+      <c r="E4">
+        <v>-1.782</v>
+      </c>
+      <c r="F4">
+        <v>2.918</v>
+      </c>
+      <c r="G4">
+        <v>1.42</v>
+      </c>
+      <c r="H4">
+        <v>141.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1.72</v>
+      </c>
+      <c r="K4">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L4">
+        <v>1.65</v>
+      </c>
+      <c r="M4">
+        <v>0.1380214</v>
+      </c>
+      <c r="N4">
+        <v>1.5119786</v>
+      </c>
+      <c r="O4">
+        <v>0.3477550779999999</v>
+      </c>
+      <c r="P4">
+        <v>1.164223522</v>
+      </c>
+      <c r="Q4">
+        <v>1.234223522</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1270092924548889</v>
+      </c>
+      <c r="T4">
+        <v>0.5148713667284056</v>
+      </c>
+      <c r="U4">
+        <v>0.0473</v>
+      </c>
+      <c r="V4">
+        <v>0.23</v>
+      </c>
+      <c r="W4">
+        <v>0.036421</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>11.95466789932576</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1251056640448174</v>
+      </c>
+      <c r="C5">
+        <v>144.8417058688188</v>
+      </c>
+      <c r="D5">
+        <v>147.7987058688189</v>
+      </c>
+      <c r="E5">
+        <v>-0.3230000000000013</v>
+      </c>
+      <c r="F5">
+        <v>4.376999999999999</v>
+      </c>
+      <c r="G5">
+        <v>1.42</v>
+      </c>
+      <c r="H5">
+        <v>141.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1.72</v>
+      </c>
+      <c r="K5">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L5">
+        <v>1.65</v>
+      </c>
+      <c r="M5">
+        <v>0.231981</v>
+      </c>
+      <c r="N5">
+        <v>1.418019</v>
+      </c>
+      <c r="O5">
+        <v>0.32614437</v>
+      </c>
+      <c r="P5">
+        <v>1.09187463</v>
+      </c>
+      <c r="Q5">
+        <v>1.16187463</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.127712746437956</v>
+      </c>
+      <c r="T5">
+        <v>0.5189773775988309</v>
+      </c>
+      <c r="U5">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V5">
+        <v>0.23</v>
+      </c>
+      <c r="W5">
+        <v>0.04081000000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>7.112651467146017</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1249876214838435</v>
+      </c>
+      <c r="C6">
+        <v>143.5851309670987</v>
+      </c>
+      <c r="D6">
+        <v>148.0011309670987</v>
+      </c>
+      <c r="E6">
+        <v>1.135999999999999</v>
+      </c>
+      <c r="F6">
+        <v>5.835999999999999</v>
+      </c>
+      <c r="G6">
+        <v>1.42</v>
+      </c>
+      <c r="H6">
+        <v>141.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1.72</v>
+      </c>
+      <c r="K6">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L6">
+        <v>1.65</v>
+      </c>
+      <c r="M6">
+        <v>0.32098</v>
+      </c>
+      <c r="N6">
+        <v>1.32902</v>
+      </c>
+      <c r="O6">
+        <v>0.3056746</v>
+      </c>
+      <c r="P6">
+        <v>1.0233454</v>
+      </c>
+      <c r="Q6">
+        <v>1.0933454</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.128430855712337</v>
+      </c>
+      <c r="T6">
+        <v>0.52316893036239</v>
+      </c>
+      <c r="U6">
+        <v>0.055</v>
+      </c>
+      <c r="V6">
+        <v>0.23</v>
+      </c>
+      <c r="W6">
+        <v>0.04235</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>5.140507196710075</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1251313789228698</v>
+      </c>
+      <c r="C7">
+        <v>141.8796821807331</v>
+      </c>
+      <c r="D7">
+        <v>147.7546821807331</v>
+      </c>
+      <c r="E7">
+        <v>2.594999999999999</v>
+      </c>
+      <c r="F7">
+        <v>7.294999999999999</v>
+      </c>
+      <c r="G7">
+        <v>1.42</v>
+      </c>
+      <c r="H7">
+        <v>141.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1.72</v>
+      </c>
+      <c r="K7">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L7">
+        <v>1.65</v>
+      </c>
+      <c r="M7">
+        <v>0.459585</v>
+      </c>
+      <c r="N7">
+        <v>1.190415</v>
+      </c>
+      <c r="O7">
+        <v>0.27379545</v>
+      </c>
+      <c r="P7">
+        <v>0.9166195500000001</v>
+      </c>
+      <c r="Q7">
+        <v>0.9866195500000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.129164083076705</v>
+      </c>
+      <c r="T7">
+        <v>0.5274487263420242</v>
+      </c>
+      <c r="U7">
+        <v>0.063</v>
+      </c>
+      <c r="V7">
+        <v>0.23</v>
+      </c>
+      <c r="W7">
+        <v>0.04851</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>3.59019550246418</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1263408163618959</v>
+      </c>
+      <c r="C8">
+        <v>138.3793481853766</v>
+      </c>
+      <c r="D8">
+        <v>145.7133481853766</v>
+      </c>
+      <c r="E8">
+        <v>4.053999999999998</v>
+      </c>
+      <c r="F8">
+        <v>8.753999999999998</v>
+      </c>
+      <c r="G8">
+        <v>1.42</v>
+      </c>
+      <c r="H8">
+        <v>141.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1.72</v>
+      </c>
+      <c r="K8">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L8">
+        <v>1.65</v>
+      </c>
+      <c r="M8">
+        <v>0.8001155999999999</v>
+      </c>
+      <c r="N8">
+        <v>0.8498844</v>
+      </c>
+      <c r="O8">
+        <v>0.195473412</v>
+      </c>
+      <c r="P8">
+        <v>0.654410988</v>
+      </c>
+      <c r="Q8">
+        <v>0.724410988</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1299129110232936</v>
+      </c>
+      <c r="T8">
+        <v>0.5318195818105866</v>
+      </c>
+      <c r="U8">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V8">
+        <v>0.23</v>
+      </c>
+      <c r="W8">
+        <v>0.07037800000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>2.062202011809294</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1329405063991306</v>
+      </c>
+      <c r="C9">
+        <v>126.705160599345</v>
+      </c>
+      <c r="D9">
+        <v>135.498160599345</v>
+      </c>
+      <c r="E9">
+        <v>5.512999999999999</v>
+      </c>
+      <c r="F9">
+        <v>10.213</v>
+      </c>
+      <c r="G9">
+        <v>1.42</v>
+      </c>
+      <c r="H9">
+        <v>141.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1.72</v>
+      </c>
+      <c r="K9">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L9">
+        <v>1.65</v>
+      </c>
+      <c r="M9">
+        <v>2.0078758</v>
+      </c>
+      <c r="N9">
+        <v>-0.3578758</v>
+      </c>
+      <c r="O9">
+        <v>-0.08231143399999999</v>
+      </c>
+      <c r="P9">
+        <v>-0.275564366</v>
+      </c>
+      <c r="Q9">
+        <v>-0.2055643659999999</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1309458097211461</v>
+      </c>
+      <c r="T9">
+        <v>0.5378485380515327</v>
+      </c>
+      <c r="U9">
+        <v>0.1966</v>
+      </c>
+      <c r="V9">
+        <v>0.189005714397275</v>
+      </c>
+      <c r="W9">
+        <v>0.1594414765494957</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>0.821763975640326</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1359869414104386</v>
+      </c>
+      <c r="C10">
+        <v>120.9988169292277</v>
+      </c>
+      <c r="D10">
+        <v>131.2508169292277</v>
+      </c>
+      <c r="E10">
+        <v>6.971999999999999</v>
+      </c>
+      <c r="F10">
+        <v>11.672</v>
+      </c>
+      <c r="G10">
+        <v>1.42</v>
+      </c>
+      <c r="H10">
+        <v>141.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1.72</v>
+      </c>
+      <c r="K10">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L10">
+        <v>1.65</v>
+      </c>
+      <c r="M10">
+        <v>2.4954736</v>
+      </c>
+      <c r="N10">
+        <v>-0.8454735999999996</v>
+      </c>
+      <c r="O10">
+        <v>-0.1944589279999999</v>
+      </c>
+      <c r="P10">
+        <v>-0.6510146719999997</v>
+      </c>
+      <c r="Q10">
+        <v>-0.5810146719999997</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1320478674477977</v>
+      </c>
+      <c r="T10">
+        <v>0.5442811706250781</v>
+      </c>
+      <c r="U10">
+        <v>0.2138</v>
+      </c>
+      <c r="V10">
+        <v>0.1520753415303612</v>
+      </c>
+      <c r="W10">
+        <v>0.1812862919808088</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>0.6611971370885271</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1377369414104386</v>
+      </c>
+      <c r="C11">
+        <v>117.2182479949984</v>
+      </c>
+      <c r="D11">
+        <v>128.9292479949984</v>
+      </c>
+      <c r="E11">
+        <v>8.430999999999997</v>
+      </c>
+      <c r="F11">
+        <v>13.131</v>
+      </c>
+      <c r="G11">
+        <v>1.42</v>
+      </c>
+      <c r="H11">
+        <v>141.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1.72</v>
+      </c>
+      <c r="K11">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L11">
+        <v>1.65</v>
+      </c>
+      <c r="M11">
+        <v>2.807407799999999</v>
+      </c>
+      <c r="N11">
+        <v>-1.157407799999999</v>
+      </c>
+      <c r="O11">
+        <v>-0.2662037939999998</v>
+      </c>
+      <c r="P11">
+        <v>-0.8912040059999995</v>
+      </c>
+      <c r="Q11">
+        <v>-0.8212040059999994</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1330725692878834</v>
+      </c>
+      <c r="T11">
+        <v>0.5502622823901887</v>
+      </c>
+      <c r="U11">
+        <v>0.2138</v>
+      </c>
+      <c r="V11">
+        <v>0.1351780813603211</v>
+      </c>
+      <c r="W11">
+        <v>0.1848989262051633</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.5877307885231353</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1394869414104386</v>
+      </c>
+      <c r="C12">
+        <v>113.5183796079897</v>
+      </c>
+      <c r="D12">
+        <v>126.6883796079897</v>
+      </c>
+      <c r="E12">
+        <v>9.889999999999997</v>
+      </c>
+      <c r="F12">
+        <v>14.59</v>
+      </c>
+      <c r="G12">
+        <v>1.42</v>
+      </c>
+      <c r="H12">
+        <v>141.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1.72</v>
+      </c>
+      <c r="K12">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L12">
+        <v>1.65</v>
+      </c>
+      <c r="M12">
+        <v>3.119342</v>
+      </c>
+      <c r="N12">
+        <v>-1.469342</v>
+      </c>
+      <c r="O12">
+        <v>-0.3379486599999999</v>
+      </c>
+      <c r="P12">
+        <v>-1.13139334</v>
+      </c>
+      <c r="Q12">
+        <v>-1.06139334</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.134120042279971</v>
+      </c>
+      <c r="T12">
+        <v>0.5563763077500797</v>
+      </c>
+      <c r="U12">
+        <v>0.2138</v>
+      </c>
+      <c r="V12">
+        <v>0.121660273224289</v>
+      </c>
+      <c r="W12">
+        <v>0.187789033584647</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.5289577096708216</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1440975521386384</v>
+      </c>
+      <c r="C13">
+        <v>106.5121395222013</v>
+      </c>
+      <c r="D13">
+        <v>121.1411395222013</v>
+      </c>
+      <c r="E13">
+        <v>11.349</v>
+      </c>
+      <c r="F13">
+        <v>16.049</v>
+      </c>
+      <c r="G13">
+        <v>1.42</v>
+      </c>
+      <c r="H13">
+        <v>141.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1.72</v>
+      </c>
+      <c r="K13">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L13">
+        <v>1.65</v>
+      </c>
+      <c r="M13">
+        <v>3.832501199999999</v>
+      </c>
+      <c r="N13">
+        <v>-2.182501199999999</v>
+      </c>
+      <c r="O13">
+        <v>-0.5019752759999998</v>
+      </c>
+      <c r="P13">
+        <v>-1.680525924</v>
+      </c>
+      <c r="Q13">
+        <v>-1.610525924</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1353153357080604</v>
+      </c>
+      <c r="T13">
+        <v>0.5633531504821149</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>0.09902149541401319</v>
+      </c>
+      <c r="W13">
+        <v>0.2151536668951337</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.4305282409304921</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1460975521386384</v>
+      </c>
+      <c r="C14">
+        <v>102.7950984558836</v>
+      </c>
+      <c r="D14">
+        <v>118.8830984558836</v>
+      </c>
+      <c r="E14">
+        <v>12.808</v>
+      </c>
+      <c r="F14">
+        <v>17.508</v>
+      </c>
+      <c r="G14">
+        <v>1.42</v>
+      </c>
+      <c r="H14">
+        <v>141.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1.72</v>
+      </c>
+      <c r="K14">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L14">
+        <v>1.65</v>
+      </c>
+      <c r="M14">
+        <v>4.180910399999999</v>
+      </c>
+      <c r="N14">
+        <v>-2.530910399999999</v>
+      </c>
+      <c r="O14">
+        <v>-0.5821093919999998</v>
+      </c>
+      <c r="P14">
+        <v>-1.948801008</v>
+      </c>
+      <c r="Q14">
+        <v>-1.878801007999999</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1364121008865611</v>
+      </c>
+      <c r="T14">
+        <v>0.5697548908285026</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>0.09076970412951209</v>
+      </c>
+      <c r="W14">
+        <v>0.2171241946538725</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.3946508875196177</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1480975521386384</v>
+      </c>
+      <c r="C15">
+        <v>99.16069569288148</v>
+      </c>
+      <c r="D15">
+        <v>116.7076956928815</v>
+      </c>
+      <c r="E15">
+        <v>14.267</v>
+      </c>
+      <c r="F15">
+        <v>18.967</v>
+      </c>
+      <c r="G15">
+        <v>1.42</v>
+      </c>
+      <c r="H15">
+        <v>141.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1.72</v>
+      </c>
+      <c r="K15">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L15">
+        <v>1.65</v>
+      </c>
+      <c r="M15">
+        <v>4.5293196</v>
+      </c>
+      <c r="N15">
+        <v>-2.8793196</v>
+      </c>
+      <c r="O15">
+        <v>-0.662243508</v>
+      </c>
+      <c r="P15">
+        <v>-2.217076092</v>
+      </c>
+      <c r="Q15">
+        <v>-2.147076092</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.137534079057671</v>
+      </c>
+      <c r="T15">
+        <v>0.5763037976196349</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>0.08378741919647269</v>
+      </c>
+      <c r="W15">
+        <v>0.2187915642958823</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.3642931269411855</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1500975521386384</v>
+      </c>
+      <c r="C16">
+        <v>95.60447624015707</v>
+      </c>
+      <c r="D16">
+        <v>114.6104762401571</v>
+      </c>
+      <c r="E16">
+        <v>15.726</v>
+      </c>
+      <c r="F16">
+        <v>20.426</v>
+      </c>
+      <c r="G16">
+        <v>1.42</v>
+      </c>
+      <c r="H16">
+        <v>141.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1.72</v>
+      </c>
+      <c r="K16">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L16">
+        <v>1.65</v>
+      </c>
+      <c r="M16">
+        <v>4.8777288</v>
+      </c>
+      <c r="N16">
+        <v>-3.2277288</v>
+      </c>
+      <c r="O16">
+        <v>-0.742377624</v>
+      </c>
+      <c r="P16">
+        <v>-2.485351176</v>
+      </c>
+      <c r="Q16">
+        <v>-2.415351176</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.138682149744388</v>
+      </c>
+      <c r="T16">
+        <v>0.5830050045687003</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>0.07780260353958178</v>
+      </c>
+      <c r="W16">
+        <v>0.2202207382747479</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.3382721893025294</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1520975521386384</v>
+      </c>
+      <c r="C17">
+        <v>92.12229967408416</v>
+      </c>
+      <c r="D17">
+        <v>112.5872996740842</v>
+      </c>
+      <c r="E17">
+        <v>17.185</v>
+      </c>
+      <c r="F17">
+        <v>21.88499999999999</v>
+      </c>
+      <c r="G17">
+        <v>1.42</v>
+      </c>
+      <c r="H17">
+        <v>141.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1.72</v>
+      </c>
+      <c r="K17">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L17">
+        <v>1.65</v>
+      </c>
+      <c r="M17">
+        <v>5.226137999999999</v>
+      </c>
+      <c r="N17">
+        <v>-3.576137999999999</v>
+      </c>
+      <c r="O17">
+        <v>-0.8225117399999997</v>
+      </c>
+      <c r="P17">
+        <v>-2.753626259999999</v>
+      </c>
+      <c r="Q17">
+        <v>-2.683626259999999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1398572338590279</v>
+      </c>
+      <c r="T17">
+        <v>0.5898638869753909</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0.07261576330360967</v>
+      </c>
+      <c r="W17">
+        <v>0.221459355723098</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.3157207100156942</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1540975521386384</v>
+      </c>
+      <c r="C18">
+        <v>88.71031285717925</v>
+      </c>
+      <c r="D18">
+        <v>110.6343128571792</v>
+      </c>
+      <c r="E18">
+        <v>18.644</v>
+      </c>
+      <c r="F18">
+        <v>23.344</v>
+      </c>
+      <c r="G18">
+        <v>1.42</v>
+      </c>
+      <c r="H18">
+        <v>141.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1.72</v>
+      </c>
+      <c r="K18">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L18">
+        <v>1.65</v>
+      </c>
+      <c r="M18">
+        <v>5.5745472</v>
+      </c>
+      <c r="N18">
+        <v>-3.9245472</v>
+      </c>
+      <c r="O18">
+        <v>-0.9026458559999998</v>
+      </c>
+      <c r="P18">
+        <v>-3.021901344</v>
+      </c>
+      <c r="Q18">
+        <v>-2.951901343999999</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1410602961668735</v>
+      </c>
+      <c r="T18">
+        <v>0.5968860761060504</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0.06807727809713406</v>
+      </c>
+      <c r="W18">
+        <v>0.2225431459904044</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.2959881656397133</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1560975521386384</v>
+      </c>
+      <c r="C19">
+        <v>85.36492544601799</v>
+      </c>
+      <c r="D19">
+        <v>108.747925446018</v>
+      </c>
+      <c r="E19">
+        <v>20.103</v>
+      </c>
+      <c r="F19">
+        <v>24.803</v>
+      </c>
+      <c r="G19">
+        <v>1.42</v>
+      </c>
+      <c r="H19">
+        <v>141.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1.72</v>
+      </c>
+      <c r="K19">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L19">
+        <v>1.65</v>
+      </c>
+      <c r="M19">
+        <v>5.922956399999999</v>
+      </c>
+      <c r="N19">
+        <v>-4.2729564</v>
+      </c>
+      <c r="O19">
+        <v>-0.9827799719999999</v>
+      </c>
+      <c r="P19">
+        <v>-3.290176428</v>
+      </c>
+      <c r="Q19">
+        <v>-3.220176428</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1422923479279202</v>
+      </c>
+      <c r="T19">
+        <v>0.6040774746133523</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.06407273232671441</v>
+      </c>
+      <c r="W19">
+        <v>0.2234994315203806</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.2785770970726713</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1580975521386385</v>
+      </c>
+      <c r="C20">
+        <v>82.08278786278171</v>
+      </c>
+      <c r="D20">
+        <v>106.9247878627817</v>
+      </c>
+      <c r="E20">
+        <v>21.56199999999999</v>
+      </c>
+      <c r="F20">
+        <v>26.26199999999999</v>
+      </c>
+      <c r="G20">
+        <v>1.42</v>
+      </c>
+      <c r="H20">
+        <v>141.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1.72</v>
+      </c>
+      <c r="K20">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L20">
+        <v>1.65</v>
+      </c>
+      <c r="M20">
+        <v>6.271365599999998</v>
+      </c>
+      <c r="N20">
+        <v>-4.621365599999999</v>
+      </c>
+      <c r="O20">
+        <v>-1.062914088</v>
+      </c>
+      <c r="P20">
+        <v>-3.558451512</v>
+      </c>
+      <c r="Q20">
+        <v>-3.488451511999999</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1435544497319192</v>
+      </c>
+      <c r="T20">
+        <v>0.6114442730842468</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.06051313608634139</v>
+      </c>
+      <c r="W20">
+        <v>0.2243494631025817</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.2631005916797451</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1600975521386384</v>
+      </c>
+      <c r="C21">
+        <v>78.86077144608487</v>
+      </c>
+      <c r="D21">
+        <v>105.1617714460849</v>
+      </c>
+      <c r="E21">
+        <v>23.021</v>
+      </c>
+      <c r="F21">
+        <v>27.721</v>
+      </c>
+      <c r="G21">
+        <v>1.42</v>
+      </c>
+      <c r="H21">
+        <v>141.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1.72</v>
+      </c>
+      <c r="K21">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L21">
+        <v>1.65</v>
+      </c>
+      <c r="M21">
+        <v>6.619774799999999</v>
+      </c>
+      <c r="N21">
+        <v>-4.9697748</v>
+      </c>
+      <c r="O21">
+        <v>-1.143048204</v>
+      </c>
+      <c r="P21">
+        <v>-3.826726596</v>
+      </c>
+      <c r="Q21">
+        <v>-3.756726596</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1448477145434243</v>
+      </c>
+      <c r="T21">
+        <v>0.6189929678136818</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.05732823418706025</v>
+      </c>
+      <c r="W21">
+        <v>0.22511001767613</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.2492531921176533</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1620975521386385</v>
+      </c>
+      <c r="C22">
+        <v>75.69595053363335</v>
+      </c>
+      <c r="D22">
+        <v>103.4559505336333</v>
+      </c>
+      <c r="E22">
+        <v>24.48</v>
+      </c>
+      <c r="F22">
+        <v>29.18</v>
+      </c>
+      <c r="G22">
+        <v>1.42</v>
+      </c>
+      <c r="H22">
+        <v>141.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1.72</v>
+      </c>
+      <c r="K22">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L22">
+        <v>1.65</v>
+      </c>
+      <c r="M22">
+        <v>6.968183999999999</v>
+      </c>
+      <c r="N22">
+        <v>-5.318183999999999</v>
+      </c>
+      <c r="O22">
+        <v>-1.22318232</v>
+      </c>
+      <c r="P22">
+        <v>-4.095001679999999</v>
+      </c>
+      <c r="Q22">
+        <v>-4.025001679999999</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1461733109752172</v>
+      </c>
+      <c r="T22">
+        <v>0.6267303799113529</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.05446182247770725</v>
+      </c>
+      <c r="W22">
+        <v>0.2257945167923235</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.2367905325117707</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1640975521386384</v>
+      </c>
+      <c r="C23">
+        <v>72.58558626086354</v>
+      </c>
+      <c r="D23">
+        <v>101.8045862608635</v>
+      </c>
+      <c r="E23">
+        <v>25.939</v>
+      </c>
+      <c r="F23">
+        <v>30.639</v>
+      </c>
+      <c r="G23">
+        <v>1.42</v>
+      </c>
+      <c r="H23">
+        <v>141.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1.72</v>
+      </c>
+      <c r="K23">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L23">
+        <v>1.65</v>
+      </c>
+      <c r="M23">
+        <v>7.3165932</v>
+      </c>
+      <c r="N23">
+        <v>-5.666593199999999</v>
+      </c>
+      <c r="O23">
+        <v>-1.303316436</v>
+      </c>
+      <c r="P23">
+        <v>-4.363276764</v>
+      </c>
+      <c r="Q23">
+        <v>-4.293276764</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1475324668103465</v>
+      </c>
+      <c r="T23">
+        <v>0.6346636758595978</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.05186840235972118</v>
+      </c>
+      <c r="W23">
+        <v>0.2264138255164986</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.2255147928683531</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1660975521386384</v>
+      </c>
+      <c r="C24">
+        <v>69.52711188683961</v>
+      </c>
+      <c r="D24">
+        <v>100.2051118868396</v>
+      </c>
+      <c r="E24">
+        <v>27.39799999999999</v>
+      </c>
+      <c r="F24">
+        <v>32.09799999999999</v>
+      </c>
+      <c r="G24">
+        <v>1.42</v>
+      </c>
+      <c r="H24">
+        <v>141.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1.72</v>
+      </c>
+      <c r="K24">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L24">
+        <v>1.65</v>
+      </c>
+      <c r="M24">
+        <v>7.665002399999999</v>
+      </c>
+      <c r="N24">
+        <v>-6.015002399999998</v>
+      </c>
+      <c r="O24">
+        <v>-1.383450552</v>
+      </c>
+      <c r="P24">
+        <v>-4.631551847999999</v>
+      </c>
+      <c r="Q24">
+        <v>-4.561551847999999</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1489264727950945</v>
+      </c>
+      <c r="T24">
+        <v>0.6428003896526696</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.04951074770700659</v>
+      </c>
+      <c r="W24">
+        <v>0.2269768334475668</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.2152641204652461</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1680975521386384</v>
+      </c>
+      <c r="C25">
+        <v>66.51811948204301</v>
+      </c>
+      <c r="D25">
+        <v>98.65511948204299</v>
+      </c>
+      <c r="E25">
+        <v>28.857</v>
+      </c>
+      <c r="F25">
+        <v>33.557</v>
+      </c>
+      <c r="G25">
+        <v>1.42</v>
+      </c>
+      <c r="H25">
+        <v>141.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1.72</v>
+      </c>
+      <c r="K25">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L25">
+        <v>1.65</v>
+      </c>
+      <c r="M25">
+        <v>8.0134116</v>
+      </c>
+      <c r="N25">
+        <v>-6.363411599999999</v>
+      </c>
+      <c r="O25">
+        <v>-1.463584668</v>
+      </c>
+      <c r="P25">
+        <v>-4.899826932</v>
+      </c>
+      <c r="Q25">
+        <v>-4.829826932</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1503566867274984</v>
+      </c>
+      <c r="T25">
+        <v>0.6511484466611458</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.04735810650235413</v>
+      </c>
+      <c r="W25">
+        <v>0.2274908841672378</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.2059048108798006</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1700975521386384</v>
+      </c>
+      <c r="C26">
+        <v>63.55634783283706</v>
+      </c>
+      <c r="D26">
+        <v>97.15234783283705</v>
+      </c>
+      <c r="E26">
+        <v>30.31599999999999</v>
+      </c>
+      <c r="F26">
+        <v>35.01599999999999</v>
+      </c>
+      <c r="G26">
+        <v>1.42</v>
+      </c>
+      <c r="H26">
+        <v>141.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1.72</v>
+      </c>
+      <c r="K26">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L26">
+        <v>1.65</v>
+      </c>
+      <c r="M26">
+        <v>8.361820799999998</v>
+      </c>
+      <c r="N26">
+        <v>-6.711820799999998</v>
+      </c>
+      <c r="O26">
+        <v>-1.543718784</v>
+      </c>
+      <c r="P26">
+        <v>-5.168102015999999</v>
+      </c>
+      <c r="Q26">
+        <v>-5.098102015999999</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1518245378686496</v>
+      </c>
+      <c r="T26">
+        <v>0.6597161893803715</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.04538485206475604</v>
+      </c>
+      <c r="W26">
+        <v>0.2279620973269363</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.197325443759809</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1720975521386384</v>
+      </c>
+      <c r="C27">
+        <v>60.63967143482199</v>
+      </c>
+      <c r="D27">
+        <v>95.69467143482198</v>
+      </c>
+      <c r="E27">
+        <v>31.775</v>
+      </c>
+      <c r="F27">
+        <v>36.47499999999999</v>
+      </c>
+      <c r="G27">
+        <v>1.42</v>
+      </c>
+      <c r="H27">
+        <v>141.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1.72</v>
+      </c>
+      <c r="K27">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L27">
+        <v>1.65</v>
+      </c>
+      <c r="M27">
+        <v>8.710229999999999</v>
+      </c>
+      <c r="N27">
+        <v>-7.060229999999999</v>
+      </c>
+      <c r="O27">
+        <v>-1.6238529</v>
+      </c>
+      <c r="P27">
+        <v>-5.4363771</v>
+      </c>
+      <c r="Q27">
+        <v>-5.366377099999999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1533315317068983</v>
+      </c>
+      <c r="T27">
+        <v>0.6685124052387764</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.04356945798216579</v>
+      </c>
+      <c r="W27">
+        <v>0.2283956134338588</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.1894324260094166</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1740975521386384</v>
+      </c>
+      <c r="C28">
+        <v>57.76609046240701</v>
+      </c>
+      <c r="D28">
+        <v>94.280090462407</v>
+      </c>
+      <c r="E28">
+        <v>33.23399999999999</v>
+      </c>
+      <c r="F28">
+        <v>37.934</v>
+      </c>
+      <c r="G28">
+        <v>1.42</v>
+      </c>
+      <c r="H28">
+        <v>141.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1.72</v>
+      </c>
+      <c r="K28">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L28">
+        <v>1.65</v>
+      </c>
+      <c r="M28">
+        <v>9.0586392</v>
+      </c>
+      <c r="N28">
+        <v>-7.4086392</v>
+      </c>
+      <c r="O28">
+        <v>-1.703987016</v>
+      </c>
+      <c r="P28">
+        <v>-5.704652184</v>
+      </c>
+      <c r="Q28">
+        <v>-5.634652184</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1548792551083429</v>
+      </c>
+      <c r="T28">
+        <v>0.677546356660922</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.04189370959823634</v>
+      </c>
+      <c r="W28">
+        <v>0.2287957821479412</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.1821465634705929</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1760975521386385</v>
+      </c>
+      <c r="C29">
+        <v>54.93372161505557</v>
+      </c>
+      <c r="D29">
+        <v>92.90672161505556</v>
+      </c>
+      <c r="E29">
+        <v>34.69299999999999</v>
+      </c>
+      <c r="F29">
+        <v>39.39299999999999</v>
+      </c>
+      <c r="G29">
+        <v>1.42</v>
+      </c>
+      <c r="H29">
+        <v>141.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1.72</v>
+      </c>
+      <c r="K29">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L29">
+        <v>1.65</v>
+      </c>
+      <c r="M29">
+        <v>9.407048399999999</v>
+      </c>
+      <c r="N29">
+        <v>-7.757048399999999</v>
+      </c>
+      <c r="O29">
+        <v>-1.784121131999999</v>
+      </c>
+      <c r="P29">
+        <v>-5.972927267999999</v>
+      </c>
+      <c r="Q29">
+        <v>-5.902927267999999</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.156469381890649</v>
+      </c>
+      <c r="T29">
+        <v>0.6868278136014826</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.04034209072422758</v>
+      </c>
+      <c r="W29">
+        <v>0.2291663087350545</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.1754003944531635</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1780975521386384</v>
+      </c>
+      <c r="C30">
+        <v>52.14078975209522</v>
+      </c>
+      <c r="D30">
+        <v>91.57278975209522</v>
+      </c>
+      <c r="E30">
+        <v>36.15199999999999</v>
+      </c>
+      <c r="F30">
+        <v>40.852</v>
+      </c>
+      <c r="G30">
+        <v>1.42</v>
+      </c>
+      <c r="H30">
+        <v>141.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1.72</v>
+      </c>
+      <c r="K30">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L30">
+        <v>1.65</v>
+      </c>
+      <c r="M30">
+        <v>9.7554576</v>
+      </c>
+      <c r="N30">
+        <v>-8.105457599999999</v>
+      </c>
+      <c r="O30">
+        <v>-1.864255248</v>
+      </c>
+      <c r="P30">
+        <v>-6.241202352</v>
+      </c>
+      <c r="Q30">
+        <v>-6.171202352</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1581036788613524</v>
+      </c>
+      <c r="T30">
+        <v>0.6963670887903921</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.03890130176979089</v>
+      </c>
+      <c r="W30">
+        <v>0.2295103691373739</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.1691360946512648</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1800975521386384</v>
+      </c>
+      <c r="C31">
+        <v>49.38562023795892</v>
+      </c>
+      <c r="D31">
+        <v>90.27662023795891</v>
+      </c>
+      <c r="E31">
+        <v>37.61099999999999</v>
+      </c>
+      <c r="F31">
+        <v>42.31099999999999</v>
+      </c>
+      <c r="G31">
+        <v>1.42</v>
+      </c>
+      <c r="H31">
+        <v>141.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1.72</v>
+      </c>
+      <c r="K31">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L31">
+        <v>1.65</v>
+      </c>
+      <c r="M31">
+        <v>10.1038668</v>
+      </c>
+      <c r="N31">
+        <v>-8.453866799999998</v>
+      </c>
+      <c r="O31">
+        <v>-1.944389363999999</v>
+      </c>
+      <c r="P31">
+        <v>-6.509477435999999</v>
+      </c>
+      <c r="Q31">
+        <v>-6.439477435999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1597840123664419</v>
+      </c>
+      <c r="T31">
+        <v>0.706175075956454</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.03755987757083259</v>
+      </c>
+      <c r="W31">
+        <v>0.2298307012360852</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.1633038155253591</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1820975521386384</v>
+      </c>
+      <c r="C32">
+        <v>46.66663192845009</v>
+      </c>
+      <c r="D32">
+        <v>89.01663192845008</v>
+      </c>
+      <c r="E32">
+        <v>39.06999999999999</v>
+      </c>
+      <c r="F32">
+        <v>43.76999999999999</v>
+      </c>
+      <c r="G32">
+        <v>1.42</v>
+      </c>
+      <c r="H32">
+        <v>141.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1.72</v>
+      </c>
+      <c r="K32">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L32">
+        <v>1.65</v>
+      </c>
+      <c r="M32">
+        <v>10.452276</v>
+      </c>
+      <c r="N32">
+        <v>-8.802275999999997</v>
+      </c>
+      <c r="O32">
+        <v>-2.024523479999999</v>
+      </c>
+      <c r="P32">
+        <v>-6.777752519999998</v>
+      </c>
+      <c r="Q32">
+        <v>-6.707752519999998</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1615123554002482</v>
+      </c>
+      <c r="T32">
+        <v>0.7162632913272604</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.03630788165180483</v>
+      </c>
+      <c r="W32">
+        <v>0.230129677861549</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.1578603550078471</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1840975521386385</v>
+      </c>
+      <c r="C33">
+        <v>43.98233073626599</v>
+      </c>
+      <c r="D33">
+        <v>87.79133073626598</v>
+      </c>
+      <c r="E33">
+        <v>40.52899999999999</v>
+      </c>
+      <c r="F33">
+        <v>45.22899999999999</v>
+      </c>
+      <c r="G33">
+        <v>1.42</v>
+      </c>
+      <c r="H33">
+        <v>141.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1.72</v>
+      </c>
+      <c r="K33">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L33">
+        <v>1.65</v>
+      </c>
+      <c r="M33">
+        <v>10.8006852</v>
+      </c>
+      <c r="N33">
+        <v>-9.150685199999998</v>
+      </c>
+      <c r="O33">
+        <v>-2.104657596</v>
+      </c>
+      <c r="P33">
+        <v>-7.046027603999999</v>
+      </c>
+      <c r="Q33">
+        <v>-6.976027603999999</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1632907953335851</v>
+      </c>
+      <c r="T33">
+        <v>0.7266439187378005</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.03513665966303694</v>
+      </c>
+      <c r="W33">
+        <v>0.2304093656724668</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.152768085491465</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1860975521386384</v>
+      </c>
+      <c r="C34">
+        <v>41.33130372072353</v>
+      </c>
+      <c r="D34">
+        <v>86.59930372072353</v>
+      </c>
+      <c r="E34">
+        <v>41.98799999999999</v>
+      </c>
+      <c r="F34">
+        <v>46.688</v>
+      </c>
+      <c r="G34">
+        <v>1.42</v>
+      </c>
+      <c r="H34">
+        <v>141.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1.72</v>
+      </c>
+      <c r="K34">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L34">
+        <v>1.65</v>
+      </c>
+      <c r="M34">
+        <v>11.1490944</v>
+      </c>
+      <c r="N34">
+        <v>-9.499094399999999</v>
+      </c>
+      <c r="O34">
+        <v>-2.184791712</v>
+      </c>
+      <c r="P34">
+        <v>-7.314302688</v>
+      </c>
+      <c r="Q34">
+        <v>-7.244302687999999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1651215423237849</v>
+      </c>
+      <c r="T34">
+        <v>0.7373298587192387</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.03403863904856703</v>
+      </c>
+      <c r="W34">
+        <v>0.2306715729952022</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.1479940828198567</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1880975521386384</v>
+      </c>
+      <c r="C35">
+        <v>38.7122136525313</v>
+      </c>
+      <c r="D35">
+        <v>85.43921365253129</v>
+      </c>
+      <c r="E35">
+        <v>43.44699999999999</v>
+      </c>
+      <c r="F35">
+        <v>48.14699999999999</v>
+      </c>
+      <c r="G35">
+        <v>1.42</v>
+      </c>
+      <c r="H35">
+        <v>141.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1.72</v>
+      </c>
+      <c r="K35">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L35">
+        <v>1.65</v>
+      </c>
+      <c r="M35">
+        <v>11.4975036</v>
+      </c>
+      <c r="N35">
+        <v>-9.847503599999998</v>
+      </c>
+      <c r="O35">
+        <v>-2.264925828</v>
+      </c>
+      <c r="P35">
+        <v>-7.582577771999999</v>
+      </c>
+      <c r="Q35">
+        <v>-7.512577771999998</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1670069384778712</v>
+      </c>
+      <c r="T35">
+        <v>0.748334781983705</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.03300716513800439</v>
+      </c>
+      <c r="W35">
+        <v>0.2309178889650446</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.1435094136434975</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1900975521386384</v>
+      </c>
+      <c r="C36">
+        <v>36.12379400965114</v>
+      </c>
+      <c r="D36">
+        <v>84.30979400965113</v>
+      </c>
+      <c r="E36">
+        <v>44.90599999999999</v>
+      </c>
+      <c r="F36">
+        <v>49.60599999999999</v>
+      </c>
+      <c r="G36">
+        <v>1.42</v>
+      </c>
+      <c r="H36">
+        <v>141.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1.72</v>
+      </c>
+      <c r="K36">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L36">
+        <v>1.65</v>
+      </c>
+      <c r="M36">
+        <v>11.8459128</v>
+      </c>
+      <c r="N36">
+        <v>-10.1959128</v>
+      </c>
+      <c r="O36">
+        <v>-2.345059944</v>
+      </c>
+      <c r="P36">
+        <v>-7.850852855999999</v>
+      </c>
+      <c r="Q36">
+        <v>-7.780852855999999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1689494678487481</v>
+      </c>
+      <c r="T36">
+        <v>0.7596731877713369</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.03203636616335721</v>
+      </c>
+      <c r="W36">
+        <v>0.2311497157601903</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.1392885485363358</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1920975521386384</v>
+      </c>
+      <c r="C37">
+        <v>33.56484436487921</v>
+      </c>
+      <c r="D37">
+        <v>83.2098443648792</v>
+      </c>
+      <c r="E37">
+        <v>46.36499999999999</v>
+      </c>
+      <c r="F37">
+        <v>51.065</v>
+      </c>
+      <c r="G37">
+        <v>1.42</v>
+      </c>
+      <c r="H37">
+        <v>141.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1.72</v>
+      </c>
+      <c r="K37">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L37">
+        <v>1.65</v>
+      </c>
+      <c r="M37">
+        <v>12.194322</v>
+      </c>
+      <c r="N37">
+        <v>-10.544322</v>
+      </c>
+      <c r="O37">
+        <v>-2.425194059999999</v>
+      </c>
+      <c r="P37">
+        <v>-8.11912794</v>
+      </c>
+      <c r="Q37">
+        <v>-8.04912794</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1709517673541134</v>
+      </c>
+      <c r="T37">
+        <v>0.7713604675832035</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.03112104141583271</v>
+      </c>
+      <c r="W37">
+        <v>0.2313682953098992</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.1353088757210118</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1940975521386384</v>
+      </c>
+      <c r="C38">
+        <v>31.03422612983329</v>
+      </c>
+      <c r="D38">
+        <v>82.13822612983327</v>
+      </c>
+      <c r="E38">
+        <v>47.82399999999998</v>
+      </c>
+      <c r="F38">
+        <v>52.52399999999999</v>
+      </c>
+      <c r="G38">
+        <v>1.42</v>
+      </c>
+      <c r="H38">
+        <v>141.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1.72</v>
+      </c>
+      <c r="K38">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L38">
+        <v>1.65</v>
+      </c>
+      <c r="M38">
+        <v>12.5427312</v>
+      </c>
+      <c r="N38">
+        <v>-10.8927312</v>
+      </c>
+      <c r="O38">
+        <v>-2.505328175999999</v>
+      </c>
+      <c r="P38">
+        <v>-8.387403023999997</v>
+      </c>
+      <c r="Q38">
+        <v>-8.317403023999997</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1730166387190215</v>
+      </c>
+      <c r="T38">
+        <v>0.7834129748891911</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.0302565680431707</v>
+      </c>
+      <c r="W38">
+        <v>0.2315747315512909</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.1315502958398727</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1960975521386384</v>
+      </c>
+      <c r="C39">
+        <v>28.53085862362521</v>
+      </c>
+      <c r="D39">
+        <v>81.0938586236252</v>
+      </c>
+      <c r="E39">
+        <v>49.28299999999999</v>
+      </c>
+      <c r="F39">
+        <v>53.98299999999999</v>
+      </c>
+      <c r="G39">
+        <v>1.42</v>
+      </c>
+      <c r="H39">
+        <v>141.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1.72</v>
+      </c>
+      <c r="K39">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L39">
+        <v>1.65</v>
+      </c>
+      <c r="M39">
+        <v>12.8911404</v>
+      </c>
+      <c r="N39">
+        <v>-11.2411404</v>
+      </c>
+      <c r="O39">
+        <v>-2.585462291999999</v>
+      </c>
+      <c r="P39">
+        <v>-8.655678107999998</v>
+      </c>
+      <c r="Q39">
+        <v>-8.585678107999998</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1751470615558313</v>
+      </c>
+      <c r="T39">
+        <v>0.7958481014747338</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.02943882296092284</v>
+      </c>
+      <c r="W39">
+        <v>0.2317700090769317</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.127994882438795</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1980975521386384</v>
+      </c>
+      <c r="C40">
+        <v>26.05371543768287</v>
+      </c>
+      <c r="D40">
+        <v>80.07571543768286</v>
+      </c>
+      <c r="E40">
+        <v>50.74199999999999</v>
+      </c>
+      <c r="F40">
+        <v>55.44199999999999</v>
+      </c>
+      <c r="G40">
+        <v>1.42</v>
+      </c>
+      <c r="H40">
+        <v>141.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1.72</v>
+      </c>
+      <c r="K40">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L40">
+        <v>1.65</v>
+      </c>
+      <c r="M40">
+        <v>13.2395496</v>
+      </c>
+      <c r="N40">
+        <v>-11.5895496</v>
+      </c>
+      <c r="O40">
+        <v>-2.665596407999999</v>
+      </c>
+      <c r="P40">
+        <v>-8.923953191999999</v>
+      </c>
+      <c r="Q40">
+        <v>-8.853953191999999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1773462077099576</v>
+      </c>
+      <c r="T40">
+        <v>0.8086843611759392</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.02866411709353013</v>
+      </c>
+      <c r="W40">
+        <v>0.231955008838065</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.1246265960588266</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2000975521386384</v>
+      </c>
+      <c r="C41">
+        <v>23.6018210710175</v>
+      </c>
+      <c r="D41">
+        <v>79.08282107101749</v>
+      </c>
+      <c r="E41">
+        <v>52.20099999999999</v>
+      </c>
+      <c r="F41">
+        <v>56.901</v>
+      </c>
+      <c r="G41">
+        <v>1.42</v>
+      </c>
+      <c r="H41">
+        <v>141.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1.72</v>
+      </c>
+      <c r="K41">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L41">
+        <v>1.65</v>
+      </c>
+      <c r="M41">
+        <v>13.5879588</v>
+      </c>
+      <c r="N41">
+        <v>-11.9379588</v>
+      </c>
+      <c r="O41">
+        <v>-2.745730523999999</v>
+      </c>
+      <c r="P41">
+        <v>-9.192228276</v>
+      </c>
+      <c r="Q41">
+        <v>-9.122228276</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1796174570166783</v>
+      </c>
+      <c r="T41">
+        <v>0.8219414818509546</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.02792913973215756</v>
+      </c>
+      <c r="W41">
+        <v>0.2321305214319608</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.1214310423137286</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2020975521386384</v>
+      </c>
+      <c r="C42">
+        <v>21.17424781274996</v>
+      </c>
+      <c r="D42">
+        <v>78.11424781274995</v>
+      </c>
+      <c r="E42">
+        <v>53.65999999999999</v>
+      </c>
+      <c r="F42">
+        <v>58.35999999999999</v>
+      </c>
+      <c r="G42">
+        <v>1.42</v>
+      </c>
+      <c r="H42">
+        <v>141.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1.72</v>
+      </c>
+      <c r="K42">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L42">
+        <v>1.65</v>
+      </c>
+      <c r="M42">
+        <v>13.936368</v>
+      </c>
+      <c r="N42">
+        <v>-12.286368</v>
+      </c>
+      <c r="O42">
+        <v>-2.825864639999999</v>
+      </c>
+      <c r="P42">
+        <v>-9.460503359999999</v>
+      </c>
+      <c r="Q42">
+        <v>-9.390503359999999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1819644146336229</v>
+      </c>
+      <c r="T42">
+        <v>0.8356405065484706</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.02723091123885362</v>
+      </c>
+      <c r="W42">
+        <v>0.2322972583961618</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.1183952662558854</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2040975521386384</v>
+      </c>
+      <c r="C43">
+        <v>18.7701128509541</v>
+      </c>
+      <c r="D43">
+        <v>77.16911285095409</v>
+      </c>
+      <c r="E43">
+        <v>55.11899999999999</v>
+      </c>
+      <c r="F43">
+        <v>59.819</v>
+      </c>
+      <c r="G43">
+        <v>1.42</v>
+      </c>
+      <c r="H43">
+        <v>141.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1.72</v>
+      </c>
+      <c r="K43">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L43">
+        <v>1.65</v>
+      </c>
+      <c r="M43">
+        <v>14.2847772</v>
+      </c>
+      <c r="N43">
+        <v>-12.6347772</v>
+      </c>
+      <c r="O43">
+        <v>-2.905998755999999</v>
+      </c>
+      <c r="P43">
+        <v>-9.728778444</v>
+      </c>
+      <c r="Q43">
+        <v>-9.658778443999999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1843909301358877</v>
+      </c>
+      <c r="T43">
+        <v>0.8498039049645463</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.02656674267205231</v>
+      </c>
+      <c r="W43">
+        <v>0.2324558618499139</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.1155075768350101</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2060975521386385</v>
+      </c>
+      <c r="C44">
+        <v>16.38857558887862</v>
+      </c>
+      <c r="D44">
+        <v>76.24657558887861</v>
+      </c>
+      <c r="E44">
+        <v>56.57799999999999</v>
+      </c>
+      <c r="F44">
+        <v>61.27799999999999</v>
+      </c>
+      <c r="G44">
+        <v>1.42</v>
+      </c>
+      <c r="H44">
+        <v>141.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1.72</v>
+      </c>
+      <c r="K44">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L44">
+        <v>1.65</v>
+      </c>
+      <c r="M44">
+        <v>14.6331864</v>
+      </c>
+      <c r="N44">
+        <v>-12.9831864</v>
+      </c>
+      <c r="O44">
+        <v>-2.986132872</v>
+      </c>
+      <c r="P44">
+        <v>-9.997053527999999</v>
+      </c>
+      <c r="Q44">
+        <v>-9.927053527999998</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1869011185865064</v>
+      </c>
+      <c r="T44">
+        <v>0.8644556964294522</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.02593420117986059</v>
+      </c>
+      <c r="W44">
+        <v>0.2326069127582493</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.1127573964341765</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2080975521386384</v>
+      </c>
+      <c r="C45">
+        <v>14.02883515139802</v>
+      </c>
+      <c r="D45">
+        <v>75.34583515139801</v>
+      </c>
+      <c r="E45">
+        <v>58.03699999999998</v>
+      </c>
+      <c r="F45">
+        <v>62.73699999999999</v>
+      </c>
+      <c r="G45">
+        <v>1.42</v>
+      </c>
+      <c r="H45">
+        <v>141.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1.72</v>
+      </c>
+      <c r="K45">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L45">
+        <v>1.65</v>
+      </c>
+      <c r="M45">
+        <v>14.9815956</v>
+      </c>
+      <c r="N45">
+        <v>-13.3315956</v>
+      </c>
+      <c r="O45">
+        <v>-3.066266987999999</v>
+      </c>
+      <c r="P45">
+        <v>-10.265328612</v>
+      </c>
+      <c r="Q45">
+        <v>-10.195328612</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1894993838248662</v>
+      </c>
+      <c r="T45">
+        <v>0.8796215858404951</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.02533108022218942</v>
+      </c>
+      <c r="W45">
+        <v>0.2327509380429412</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.1101351314008235</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2100975521386385</v>
+      </c>
+      <c r="C46">
+        <v>11.69012806614536</v>
+      </c>
+      <c r="D46">
+        <v>74.46612806614534</v>
+      </c>
+      <c r="E46">
+        <v>59.49599999999998</v>
+      </c>
+      <c r="F46">
+        <v>64.19599999999998</v>
+      </c>
+      <c r="G46">
+        <v>1.42</v>
+      </c>
+      <c r="H46">
+        <v>141.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1.72</v>
+      </c>
+      <c r="K46">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L46">
+        <v>1.65</v>
+      </c>
+      <c r="M46">
+        <v>15.3300048</v>
+      </c>
+      <c r="N46">
+        <v>-13.6800048</v>
+      </c>
+      <c r="O46">
+        <v>-3.146401103999999</v>
+      </c>
+      <c r="P46">
+        <v>-10.533603696</v>
+      </c>
+      <c r="Q46">
+        <v>-10.463603696</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1921904442503102</v>
+      </c>
+      <c r="T46">
+        <v>0.8953291141590756</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.0247553738535033</v>
+      </c>
+      <c r="W46">
+        <v>0.2328884167237834</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.1076320602326231</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2120975521386384</v>
+      </c>
+      <c r="C47">
+        <v>9.371726105215501</v>
+      </c>
+      <c r="D47">
+        <v>73.60672610521549</v>
+      </c>
+      <c r="E47">
+        <v>60.95499999999998</v>
+      </c>
+      <c r="F47">
+        <v>65.65499999999999</v>
+      </c>
+      <c r="G47">
+        <v>1.42</v>
+      </c>
+      <c r="H47">
+        <v>141.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1.72</v>
+      </c>
+      <c r="K47">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L47">
+        <v>1.65</v>
+      </c>
+      <c r="M47">
+        <v>15.678414</v>
+      </c>
+      <c r="N47">
+        <v>-14.028414</v>
+      </c>
+      <c r="O47">
+        <v>-3.226535219999999</v>
+      </c>
+      <c r="P47">
+        <v>-10.80187878</v>
+      </c>
+      <c r="Q47">
+        <v>-10.73187878</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1949793614184977</v>
+      </c>
+      <c r="T47">
+        <v>0.9116078253256041</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.02420525443453656</v>
+      </c>
+      <c r="W47">
+        <v>0.2330197852410327</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.1052402366718981</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2140975521386385</v>
+      </c>
+      <c r="C48">
+        <v>7.072934274614212</v>
+      </c>
+      <c r="D48">
+        <v>72.7669342746142</v>
+      </c>
+      <c r="E48">
+        <v>62.41399999999999</v>
+      </c>
+      <c r="F48">
+        <v>67.11399999999999</v>
+      </c>
+      <c r="G48">
+        <v>1.42</v>
+      </c>
+      <c r="H48">
+        <v>141.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1.72</v>
+      </c>
+      <c r="K48">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L48">
+        <v>1.65</v>
+      </c>
+      <c r="M48">
+        <v>16.0268232</v>
+      </c>
+      <c r="N48">
+        <v>-14.3768232</v>
+      </c>
+      <c r="O48">
+        <v>-3.306669335999999</v>
+      </c>
+      <c r="P48">
+        <v>-11.070153864</v>
+      </c>
+      <c r="Q48">
+        <v>-11.000153864</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1978715718151365</v>
+      </c>
+      <c r="T48">
+        <v>0.9284894517205228</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.02367905325117706</v>
+      </c>
+      <c r="W48">
+        <v>0.2331454420836189</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1029524054399004</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2160975521386385</v>
+      </c>
+      <c r="C49">
+        <v>4.79308893978731</v>
+      </c>
+      <c r="D49">
+        <v>71.9460889397873</v>
+      </c>
+      <c r="E49">
+        <v>63.87299999999999</v>
+      </c>
+      <c r="F49">
+        <v>68.57299999999999</v>
+      </c>
+      <c r="G49">
+        <v>1.42</v>
+      </c>
+      <c r="H49">
+        <v>141.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1.72</v>
+      </c>
+      <c r="K49">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L49">
+        <v>1.65</v>
+      </c>
+      <c r="M49">
+        <v>16.3752324</v>
+      </c>
+      <c r="N49">
+        <v>-14.7252324</v>
+      </c>
+      <c r="O49">
+        <v>-3.386803451999999</v>
+      </c>
+      <c r="P49">
+        <v>-11.338428948</v>
+      </c>
+      <c r="Q49">
+        <v>-11.268428948</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2008729222267429</v>
+      </c>
+      <c r="T49">
+        <v>0.94600812062091</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.023175243607535</v>
+      </c>
+      <c r="W49">
+        <v>0.2332657518265207</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1007619287284131</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2180975521386384</v>
+      </c>
+      <c r="C50">
+        <v>2.531556076604048</v>
+      </c>
+      <c r="D50">
+        <v>71.14355607660403</v>
+      </c>
+      <c r="E50">
+        <v>65.33199999999998</v>
+      </c>
+      <c r="F50">
+        <v>70.03199999999998</v>
+      </c>
+      <c r="G50">
+        <v>1.42</v>
+      </c>
+      <c r="H50">
+        <v>141.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1.72</v>
+      </c>
+      <c r="K50">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L50">
+        <v>1.65</v>
+      </c>
+      <c r="M50">
+        <v>16.7236416</v>
+      </c>
+      <c r="N50">
+        <v>-15.0736416</v>
+      </c>
+      <c r="O50">
+        <v>-3.466937567999999</v>
+      </c>
+      <c r="P50">
+        <v>-11.606704032</v>
+      </c>
+      <c r="Q50">
+        <v>-11.536704032</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2039897091926418</v>
+      </c>
+      <c r="T50">
+        <v>0.9642005844790044</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.02269242603237802</v>
+      </c>
+      <c r="W50">
+        <v>0.2333810486634681</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.09866272187990444</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2200975521386384</v>
+      </c>
+      <c r="C51">
+        <v>0.2877296381069527</v>
+      </c>
+      <c r="D51">
+        <v>70.35872963810694</v>
+      </c>
+      <c r="E51">
+        <v>66.79099999999998</v>
+      </c>
+      <c r="F51">
+        <v>71.49099999999999</v>
+      </c>
+      <c r="G51">
+        <v>1.42</v>
+      </c>
+      <c r="H51">
+        <v>141.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1.72</v>
+      </c>
+      <c r="K51">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L51">
+        <v>1.65</v>
+      </c>
+      <c r="M51">
+        <v>17.0720508</v>
+      </c>
+      <c r="N51">
+        <v>-15.4220508</v>
+      </c>
+      <c r="O51">
+        <v>-3.547071683999999</v>
+      </c>
+      <c r="P51">
+        <v>-11.874979116</v>
+      </c>
+      <c r="Q51">
+        <v>-11.804979116</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2072287230983799</v>
+      </c>
+      <c r="T51">
+        <v>0.9831064782923182</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.02222931529702337</v>
+      </c>
+      <c r="W51">
+        <v>0.2334916395070708</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.09664919694357987</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2220975521386384</v>
+      </c>
+      <c r="C52">
+        <v>-1.938969971813549</v>
+      </c>
+      <c r="D52">
+        <v>69.59103002818644</v>
+      </c>
+      <c r="E52">
+        <v>68.24999999999999</v>
+      </c>
+      <c r="F52">
+        <v>72.94999999999999</v>
+      </c>
+      <c r="G52">
+        <v>1.42</v>
+      </c>
+      <c r="H52">
+        <v>141.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1.72</v>
+      </c>
+      <c r="K52">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L52">
+        <v>1.65</v>
+      </c>
+      <c r="M52">
+        <v>17.42046</v>
+      </c>
+      <c r="N52">
+        <v>-15.77046</v>
+      </c>
+      <c r="O52">
+        <v>-3.627205799999999</v>
+      </c>
+      <c r="P52">
+        <v>-12.1432542</v>
+      </c>
+      <c r="Q52">
+        <v>-12.0732542</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2105972975603475</v>
+      </c>
+      <c r="T52">
+        <v>1.002768607858165</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.0217847289910829</v>
+      </c>
+      <c r="W52">
+        <v>0.2335978067169294</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.09471621300470834</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2240975521386385</v>
+      </c>
+      <c r="C53">
+        <v>-4.149097325898822</v>
+      </c>
+      <c r="D53">
+        <v>68.83990267410117</v>
+      </c>
+      <c r="E53">
+        <v>69.70899999999999</v>
+      </c>
+      <c r="F53">
+        <v>74.40899999999999</v>
+      </c>
+      <c r="G53">
+        <v>1.42</v>
+      </c>
+      <c r="H53">
+        <v>141.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1.72</v>
+      </c>
+      <c r="K53">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L53">
+        <v>1.65</v>
+      </c>
+      <c r="M53">
+        <v>17.7688692</v>
+      </c>
+      <c r="N53">
+        <v>-16.1188692</v>
+      </c>
+      <c r="O53">
+        <v>-3.707339916</v>
+      </c>
+      <c r="P53">
+        <v>-12.411529284</v>
+      </c>
+      <c r="Q53">
+        <v>-12.341529284</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2141033648574974</v>
+      </c>
+      <c r="T53">
+        <v>1.023233273324658</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.02135757744223813</v>
+      </c>
+      <c r="W53">
+        <v>0.2336998105067936</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.0928590323575571</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2260975521386385</v>
+      </c>
+      <c r="C54">
+        <v>-6.343183309544202</v>
+      </c>
+      <c r="D54">
+        <v>68.10481669045579</v>
+      </c>
+      <c r="E54">
+        <v>71.16799999999999</v>
+      </c>
+      <c r="F54">
+        <v>75.86799999999999</v>
+      </c>
+      <c r="G54">
+        <v>1.42</v>
+      </c>
+      <c r="H54">
+        <v>141.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1.72</v>
+      </c>
+      <c r="K54">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L54">
+        <v>1.65</v>
+      </c>
+      <c r="M54">
+        <v>18.1172784</v>
+      </c>
+      <c r="N54">
+        <v>-16.4672784</v>
+      </c>
+      <c r="O54">
+        <v>-3.787474032</v>
+      </c>
+      <c r="P54">
+        <v>-12.679804368</v>
+      </c>
+      <c r="Q54">
+        <v>-12.609804368</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2177555182920286</v>
+      </c>
+      <c r="T54">
+        <v>1.044550633185588</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.02094685479911817</v>
+      </c>
+      <c r="W54">
+        <v>0.2337978910739706</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.09107328173529627</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2280975521386384</v>
+      </c>
+      <c r="C55">
+        <v>-8.521736372127663</v>
+      </c>
+      <c r="D55">
+        <v>67.38526362787233</v>
+      </c>
+      <c r="E55">
+        <v>72.627</v>
+      </c>
+      <c r="F55">
+        <v>77.327</v>
+      </c>
+      <c r="G55">
+        <v>1.42</v>
+      </c>
+      <c r="H55">
+        <v>141.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1.72</v>
+      </c>
+      <c r="K55">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L55">
+        <v>1.65</v>
+      </c>
+      <c r="M55">
+        <v>18.4656876</v>
+      </c>
+      <c r="N55">
+        <v>-16.8156876</v>
+      </c>
+      <c r="O55">
+        <v>-3.867608148</v>
+      </c>
+      <c r="P55">
+        <v>-12.948079452</v>
+      </c>
+      <c r="Q55">
+        <v>-12.878079452</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.221563082511008</v>
+      </c>
+      <c r="T55">
+        <v>1.066775114742728</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.02055163112366311</v>
+      </c>
+      <c r="W55">
+        <v>0.2338922704876693</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.08935491792896999</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2300975521386384</v>
+      </c>
+      <c r="C56">
+        <v>-10.68524369984334</v>
+      </c>
+      <c r="D56">
+        <v>66.68075630015665</v>
+      </c>
+      <c r="E56">
+        <v>74.08599999999998</v>
+      </c>
+      <c r="F56">
+        <v>78.78599999999999</v>
+      </c>
+      <c r="G56">
+        <v>1.42</v>
+      </c>
+      <c r="H56">
+        <v>141.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1.72</v>
+      </c>
+      <c r="K56">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L56">
+        <v>1.65</v>
+      </c>
+      <c r="M56">
+        <v>18.8140968</v>
+      </c>
+      <c r="N56">
+        <v>-17.1640968</v>
+      </c>
+      <c r="O56">
+        <v>-3.947742264</v>
+      </c>
+      <c r="P56">
+        <v>-13.216354536</v>
+      </c>
+      <c r="Q56">
+        <v>-13.146354536</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2255361930003777</v>
+      </c>
+      <c r="T56">
+        <v>1.089965878106701</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.02017104536211379</v>
+      </c>
+      <c r="W56">
+        <v>0.2339831543675272</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.08770019722658162</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2320975521386384</v>
+      </c>
+      <c r="C57">
+        <v>-12.83417231572496</v>
+      </c>
+      <c r="D57">
+        <v>65.99082768427503</v>
+      </c>
+      <c r="E57">
+        <v>75.54499999999999</v>
+      </c>
+      <c r="F57">
+        <v>80.24499999999999</v>
+      </c>
+      <c r="G57">
+        <v>1.42</v>
+      </c>
+      <c r="H57">
+        <v>141.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1.72</v>
+      </c>
+      <c r="K57">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L57">
+        <v>1.65</v>
+      </c>
+      <c r="M57">
+        <v>19.162506</v>
+      </c>
+      <c r="N57">
+        <v>-17.512506</v>
+      </c>
+      <c r="O57">
+        <v>-4.027876379999999</v>
+      </c>
+      <c r="P57">
+        <v>-13.48462962</v>
+      </c>
+      <c r="Q57">
+        <v>-13.41462962</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2296858861781639</v>
+      </c>
+      <c r="T57">
+        <v>1.114187342064628</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.01980429908280263</v>
+      </c>
+      <c r="W57">
+        <v>0.2340707333790267</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.08610564818609834</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2340975521386385</v>
+      </c>
+      <c r="C58">
+        <v>-14.96897011207859</v>
+      </c>
+      <c r="D58">
+        <v>65.3150298879214</v>
+      </c>
+      <c r="E58">
+        <v>77.00399999999999</v>
+      </c>
+      <c r="F58">
+        <v>81.70399999999999</v>
+      </c>
+      <c r="G58">
+        <v>1.42</v>
+      </c>
+      <c r="H58">
+        <v>141.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1.72</v>
+      </c>
+      <c r="K58">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L58">
+        <v>1.65</v>
+      </c>
+      <c r="M58">
+        <v>19.5109152</v>
+      </c>
+      <c r="N58">
+        <v>-17.8609152</v>
+      </c>
+      <c r="O58">
+        <v>-4.108010495999999</v>
+      </c>
+      <c r="P58">
+        <v>-13.752904704</v>
+      </c>
+      <c r="Q58">
+        <v>-13.682904704</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2340242017731221</v>
+      </c>
+      <c r="T58">
+        <v>1.139509781657005</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.01945065088489544</v>
+      </c>
+      <c r="W58">
+        <v>0.234155184568687</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.08456804732563228</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2360975521386385</v>
+      </c>
+      <c r="C59">
+        <v>-17.09006682012112</v>
+      </c>
+      <c r="D59">
+        <v>64.65293317987887</v>
+      </c>
+      <c r="E59">
+        <v>78.46299999999999</v>
+      </c>
+      <c r="F59">
+        <v>83.163</v>
+      </c>
+      <c r="G59">
+        <v>1.42</v>
+      </c>
+      <c r="H59">
+        <v>141.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1.72</v>
+      </c>
+      <c r="K59">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L59">
+        <v>1.65</v>
+      </c>
+      <c r="M59">
+        <v>19.8593244</v>
+      </c>
+      <c r="N59">
+        <v>-18.2093244</v>
+      </c>
+      <c r="O59">
+        <v>-4.188144612</v>
+      </c>
+      <c r="P59">
+        <v>-14.021179788</v>
+      </c>
+      <c r="Q59">
+        <v>-13.951179788</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2385642994887761</v>
+      </c>
+      <c r="T59">
+        <v>1.166010009137401</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.01910941139568675</v>
+      </c>
+      <c r="W59">
+        <v>0.23423667255871</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.08308439737255102</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2380975521386384</v>
+      </c>
+      <c r="C60">
+        <v>-19.19787492123521</v>
+      </c>
+      <c r="D60">
+        <v>64.00412507876477</v>
+      </c>
+      <c r="E60">
+        <v>79.92199999999998</v>
+      </c>
+      <c r="F60">
+        <v>84.62199999999999</v>
+      </c>
+      <c r="G60">
+        <v>1.42</v>
+      </c>
+      <c r="H60">
+        <v>141.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1.72</v>
+      </c>
+      <c r="K60">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L60">
+        <v>1.65</v>
+      </c>
+      <c r="M60">
+        <v>20.2077336</v>
+      </c>
+      <c r="N60">
+        <v>-18.5577336</v>
+      </c>
+      <c r="O60">
+        <v>-4.268278727999999</v>
+      </c>
+      <c r="P60">
+        <v>-14.289454872</v>
+      </c>
+      <c r="Q60">
+        <v>-14.219454872</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2433205923337469</v>
+      </c>
+      <c r="T60">
+        <v>1.193772152212101</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.01877993878541629</v>
+      </c>
+      <c r="W60">
+        <v>0.2343153506180426</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.0816519077626795</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2400975521386384</v>
+      </c>
+      <c r="C61">
+        <v>-21.29279050390144</v>
+      </c>
+      <c r="D61">
+        <v>63.36820949609855</v>
+      </c>
+      <c r="E61">
+        <v>81.38099999999999</v>
+      </c>
+      <c r="F61">
+        <v>86.08099999999999</v>
+      </c>
+      <c r="G61">
+        <v>1.42</v>
+      </c>
+      <c r="H61">
+        <v>141.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1.72</v>
+      </c>
+      <c r="K61">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L61">
+        <v>1.65</v>
+      </c>
+      <c r="M61">
+        <v>20.5561428</v>
+      </c>
+      <c r="N61">
+        <v>-18.9061428</v>
+      </c>
+      <c r="O61">
+        <v>-4.348412844</v>
+      </c>
+      <c r="P61">
+        <v>-14.557729956</v>
+      </c>
+      <c r="Q61">
+        <v>-14.487729956</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2483088994638383</v>
+      </c>
+      <c r="T61">
+        <v>1.222888546168493</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.01846163473820584</v>
+      </c>
+      <c r="W61">
+        <v>0.2343913616245165</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.080267977122634</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2420975521386384</v>
+      </c>
+      <c r="C62">
+        <v>-23.37519407004851</v>
+      </c>
+      <c r="D62">
+        <v>62.74480592995148</v>
+      </c>
+      <c r="E62">
+        <v>82.83999999999997</v>
+      </c>
+      <c r="F62">
+        <v>87.53999999999998</v>
+      </c>
+      <c r="G62">
+        <v>1.42</v>
+      </c>
+      <c r="H62">
+        <v>141.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1.72</v>
+      </c>
+      <c r="K62">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L62">
+        <v>1.65</v>
+      </c>
+      <c r="M62">
+        <v>20.904552</v>
+      </c>
+      <c r="N62">
+        <v>-19.254552</v>
+      </c>
+      <c r="O62">
+        <v>-4.428546959999998</v>
+      </c>
+      <c r="P62">
+        <v>-14.82600504</v>
+      </c>
+      <c r="Q62">
+        <v>-14.75600504</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2535466219504343</v>
+      </c>
+      <c r="T62">
+        <v>1.253460759822706</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.01815394082590242</v>
+      </c>
+      <c r="W62">
+        <v>0.2344648389307745</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.0789301775039235</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2440975521386384</v>
+      </c>
+      <c r="C63">
+        <v>-25.44545129427084</v>
+      </c>
+      <c r="D63">
+        <v>62.13354870572914</v>
+      </c>
+      <c r="E63">
+        <v>84.29899999999998</v>
+      </c>
+      <c r="F63">
+        <v>88.99899999999998</v>
+      </c>
+      <c r="G63">
+        <v>1.42</v>
+      </c>
+      <c r="H63">
+        <v>141.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1.72</v>
+      </c>
+      <c r="K63">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L63">
+        <v>1.65</v>
+      </c>
+      <c r="M63">
+        <v>21.2529612</v>
+      </c>
+      <c r="N63">
+        <v>-19.6029612</v>
+      </c>
+      <c r="O63">
+        <v>-4.508681075999999</v>
+      </c>
+      <c r="P63">
+        <v>-15.094280124</v>
+      </c>
+      <c r="Q63">
+        <v>-15.024280124</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.259052945590189</v>
+      </c>
+      <c r="T63">
+        <v>1.285600779305339</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.01785633523859254</v>
+      </c>
+      <c r="W63">
+        <v>0.2345359071450241</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.07763624016779358</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2460975521386384</v>
+      </c>
+      <c r="C64">
+        <v>-27.50391373909676</v>
+      </c>
+      <c r="D64">
+        <v>61.53408626090322</v>
+      </c>
+      <c r="E64">
+        <v>85.75799999999998</v>
+      </c>
+      <c r="F64">
+        <v>90.45799999999998</v>
+      </c>
+      <c r="G64">
+        <v>1.42</v>
+      </c>
+      <c r="H64">
+        <v>141.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1.72</v>
+      </c>
+      <c r="K64">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L64">
+        <v>1.65</v>
+      </c>
+      <c r="M64">
+        <v>21.6013704</v>
+      </c>
+      <c r="N64">
+        <v>-19.9513704</v>
+      </c>
+      <c r="O64">
+        <v>-4.588815191999999</v>
+      </c>
+      <c r="P64">
+        <v>-15.362555208</v>
+      </c>
+      <c r="Q64">
+        <v>-15.292555208</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2648490757372993</v>
+      </c>
+      <c r="T64">
+        <v>1.319432378760743</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.01756832983151847</v>
+      </c>
+      <c r="W64">
+        <v>0.2346046828362334</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.07638404274573241</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2480975521386384</v>
+      </c>
+      <c r="C65">
+        <v>-29.55091952924707</v>
+      </c>
+      <c r="D65">
+        <v>60.94608047075291</v>
+      </c>
+      <c r="E65">
+        <v>87.21699999999998</v>
+      </c>
+      <c r="F65">
+        <v>91.91699999999999</v>
+      </c>
+      <c r="G65">
+        <v>1.42</v>
+      </c>
+      <c r="H65">
+        <v>141.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1.72</v>
+      </c>
+      <c r="K65">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L65">
+        <v>1.65</v>
+      </c>
+      <c r="M65">
+        <v>21.9497796</v>
+      </c>
+      <c r="N65">
+        <v>-20.2997796</v>
+      </c>
+      <c r="O65">
+        <v>-4.668949308</v>
+      </c>
+      <c r="P65">
+        <v>-15.630830292</v>
+      </c>
+      <c r="Q65">
+        <v>-15.560830292</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2709585102166857</v>
+      </c>
+      <c r="T65">
+        <v>1.355092713321844</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.0172894674532404</v>
+      </c>
+      <c r="W65">
+        <v>0.2346712751721662</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.07517159762278425</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2500975521386384</v>
+      </c>
+      <c r="C66">
+        <v>-31.5867939876011</v>
+      </c>
+      <c r="D66">
+        <v>60.36920601239889</v>
+      </c>
+      <c r="E66">
+        <v>88.67599999999999</v>
+      </c>
+      <c r="F66">
+        <v>93.37599999999999</v>
+      </c>
+      <c r="G66">
+        <v>1.42</v>
+      </c>
+      <c r="H66">
+        <v>141.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1.72</v>
+      </c>
+      <c r="K66">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L66">
+        <v>1.65</v>
+      </c>
+      <c r="M66">
+        <v>22.2981888</v>
+      </c>
+      <c r="N66">
+        <v>-20.6481888</v>
+      </c>
+      <c r="O66">
+        <v>-4.749083423999999</v>
+      </c>
+      <c r="P66">
+        <v>-15.899105376</v>
+      </c>
+      <c r="Q66">
+        <v>-15.829105376</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2774073577227048</v>
+      </c>
+      <c r="T66">
+        <v>1.392734177580784</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.01701931952428351</v>
+      </c>
+      <c r="W66">
+        <v>0.2347357864976011</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.07399704140992824</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2520975521386385</v>
+      </c>
+      <c r="C67">
+        <v>-33.61185023538365</v>
+      </c>
+      <c r="D67">
+        <v>59.80314976461634</v>
+      </c>
+      <c r="E67">
+        <v>90.13499999999999</v>
+      </c>
+      <c r="F67">
+        <v>94.83499999999999</v>
+      </c>
+      <c r="G67">
+        <v>1.42</v>
+      </c>
+      <c r="H67">
+        <v>141.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1.72</v>
+      </c>
+      <c r="K67">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L67">
+        <v>1.65</v>
+      </c>
+      <c r="M67">
+        <v>22.646598</v>
+      </c>
+      <c r="N67">
+        <v>-20.996598</v>
+      </c>
+      <c r="O67">
+        <v>-4.82921754</v>
+      </c>
+      <c r="P67">
+        <v>-16.16738046</v>
+      </c>
+      <c r="Q67">
+        <v>-16.09738046</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2842247108004964</v>
+      </c>
+      <c r="T67">
+        <v>1.432526582654521</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.01675748383929454</v>
+      </c>
+      <c r="W67">
+        <v>0.2347983128591765</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.07285862538823706</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2540975521386384</v>
+      </c>
+      <c r="C68">
+        <v>-35.6263897588995</v>
+      </c>
+      <c r="D68">
+        <v>59.24761024110048</v>
+      </c>
+      <c r="E68">
+        <v>91.59399999999998</v>
+      </c>
+      <c r="F68">
+        <v>96.29399999999998</v>
+      </c>
+      <c r="G68">
+        <v>1.42</v>
+      </c>
+      <c r="H68">
+        <v>141.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1.72</v>
+      </c>
+      <c r="K68">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L68">
+        <v>1.65</v>
+      </c>
+      <c r="M68">
+        <v>22.9950072</v>
+      </c>
+      <c r="N68">
+        <v>-21.3450072</v>
+      </c>
+      <c r="O68">
+        <v>-4.909351655999999</v>
+      </c>
+      <c r="P68">
+        <v>-16.435655544</v>
+      </c>
+      <c r="Q68">
+        <v>-16.365655544</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2914430846475698</v>
+      </c>
+      <c r="T68">
+        <v>1.474659717438477</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.0165035825690022</v>
+      </c>
+      <c r="W68">
+        <v>0.2348589444825223</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.07175470682174867</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2560975521386384</v>
+      </c>
+      <c r="C69">
+        <v>-37.63070294497074</v>
+      </c>
+      <c r="D69">
+        <v>58.70229705502925</v>
+      </c>
+      <c r="E69">
+        <v>93.05299999999998</v>
+      </c>
+      <c r="F69">
+        <v>97.75299999999999</v>
+      </c>
+      <c r="G69">
+        <v>1.42</v>
+      </c>
+      <c r="H69">
+        <v>141.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1.72</v>
+      </c>
+      <c r="K69">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L69">
+        <v>1.65</v>
+      </c>
+      <c r="M69">
+        <v>23.3434164</v>
+      </c>
+      <c r="N69">
+        <v>-21.6934164</v>
+      </c>
+      <c r="O69">
+        <v>-4.989485772</v>
+      </c>
+      <c r="P69">
+        <v>-16.703930628</v>
+      </c>
+      <c r="Q69">
+        <v>-16.633930628</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2990989356974962</v>
+      </c>
+      <c r="T69">
+        <v>1.519346375542674</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.01625726044110664</v>
+      </c>
+      <c r="W69">
+        <v>0.2349177662066637</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.07068374104828967</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2580975521386384</v>
+      </c>
+      <c r="C70">
+        <v>-39.6250695870746</v>
+      </c>
+      <c r="D70">
+        <v>58.16693041292539</v>
+      </c>
+      <c r="E70">
+        <v>94.51199999999999</v>
+      </c>
+      <c r="F70">
+        <v>99.21199999999999</v>
+      </c>
+      <c r="G70">
+        <v>1.42</v>
+      </c>
+      <c r="H70">
+        <v>141.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1.72</v>
+      </c>
+      <c r="K70">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L70">
+        <v>1.65</v>
+      </c>
+      <c r="M70">
+        <v>23.6918256</v>
+      </c>
+      <c r="N70">
+        <v>-22.0418256</v>
+      </c>
+      <c r="O70">
+        <v>-5.069619887999999</v>
+      </c>
+      <c r="P70">
+        <v>-16.972205712</v>
+      </c>
+      <c r="Q70">
+        <v>-16.902205712</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3072332774380429</v>
+      </c>
+      <c r="T70">
+        <v>1.566825949778382</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.0160181830816786</v>
+      </c>
+      <c r="W70">
+        <v>0.2349748578800952</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.06964427426816777</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2600975521386384</v>
+      </c>
+      <c r="C71">
+        <v>-41.60975936403594</v>
+      </c>
+      <c r="D71">
+        <v>57.64124063596405</v>
+      </c>
+      <c r="E71">
+        <v>95.97099999999999</v>
+      </c>
+      <c r="F71">
+        <v>100.671</v>
+      </c>
+      <c r="G71">
+        <v>1.42</v>
+      </c>
+      <c r="H71">
+        <v>141.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1.72</v>
+      </c>
+      <c r="K71">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L71">
+        <v>1.65</v>
+      </c>
+      <c r="M71">
+        <v>24.0402348</v>
+      </c>
+      <c r="N71">
+        <v>-22.3902348</v>
+      </c>
+      <c r="O71">
+        <v>-5.149754004</v>
+      </c>
+      <c r="P71">
+        <v>-17.240480796</v>
+      </c>
+      <c r="Q71">
+        <v>-17.170480796</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3158924154199153</v>
+      </c>
+      <c r="T71">
+        <v>1.617368722351879</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.01578603550078471</v>
+      </c>
+      <c r="W71">
+        <v>0.2350302947224126</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.0686349369599335</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2620975521386384</v>
+      </c>
+      <c r="C72">
+        <v>-43.58503229299467</v>
+      </c>
+      <c r="D72">
+        <v>57.12496770700533</v>
+      </c>
+      <c r="E72">
+        <v>97.42999999999999</v>
+      </c>
+      <c r="F72">
+        <v>102.13</v>
+      </c>
+      <c r="G72">
+        <v>1.42</v>
+      </c>
+      <c r="H72">
+        <v>141.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1.72</v>
+      </c>
+      <c r="K72">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L72">
+        <v>1.65</v>
+      </c>
+      <c r="M72">
+        <v>24.388644</v>
+      </c>
+      <c r="N72">
+        <v>-22.738644</v>
+      </c>
+      <c r="O72">
+        <v>-5.22988812</v>
+      </c>
+      <c r="P72">
+        <v>-17.50875588</v>
+      </c>
+      <c r="Q72">
+        <v>-17.43875588</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3251288292672458</v>
+      </c>
+      <c r="T72">
+        <v>1.671281013096941</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.01556052070791636</v>
+      </c>
+      <c r="W72">
+        <v>0.2350841476549496</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.06765443786050584</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2640975521386384</v>
+      </c>
+      <c r="C73">
+        <v>-45.55113915824682</v>
+      </c>
+      <c r="D73">
+        <v>56.61786084175316</v>
+      </c>
+      <c r="E73">
+        <v>98.88899999999998</v>
+      </c>
+      <c r="F73">
+        <v>103.589</v>
+      </c>
+      <c r="G73">
+        <v>1.42</v>
+      </c>
+      <c r="H73">
+        <v>141.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1.72</v>
+      </c>
+      <c r="K73">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L73">
+        <v>1.65</v>
+      </c>
+      <c r="M73">
+        <v>24.7370532</v>
+      </c>
+      <c r="N73">
+        <v>-23.0870532</v>
+      </c>
+      <c r="O73">
+        <v>-5.310022235999999</v>
+      </c>
+      <c r="P73">
+        <v>-17.777030964</v>
+      </c>
+      <c r="Q73">
+        <v>-17.707030964</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3350022371730129</v>
+      </c>
+      <c r="T73">
+        <v>1.728911392858905</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.01534135844442458</v>
+      </c>
+      <c r="W73">
+        <v>0.2351364836034714</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.06670155845401982</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2660975521386384</v>
+      </c>
+      <c r="C74">
+        <v>-47.50832191744536</v>
+      </c>
+      <c r="D74">
+        <v>56.11967808255461</v>
+      </c>
+      <c r="E74">
+        <v>100.348</v>
+      </c>
+      <c r="F74">
+        <v>105.048</v>
+      </c>
+      <c r="G74">
+        <v>1.42</v>
+      </c>
+      <c r="H74">
+        <v>141.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1.72</v>
+      </c>
+      <c r="K74">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L74">
+        <v>1.65</v>
+      </c>
+      <c r="M74">
+        <v>25.08546239999999</v>
+      </c>
+      <c r="N74">
+        <v>-23.4354624</v>
+      </c>
+      <c r="O74">
+        <v>-5.390156351999998</v>
+      </c>
+      <c r="P74">
+        <v>-18.045306048</v>
+      </c>
+      <c r="Q74">
+        <v>-17.975306048</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3455808885006204</v>
+      </c>
+      <c r="T74">
+        <v>1.790658228318151</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.01512828402158535</v>
+      </c>
+      <c r="W74">
+        <v>0.2351873657756454</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.06577514791993622</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2680975521386385</v>
+      </c>
+      <c r="C75">
+        <v>-49.45681408654296</v>
+      </c>
+      <c r="D75">
+        <v>55.63018591345702</v>
+      </c>
+      <c r="E75">
+        <v>101.807</v>
+      </c>
+      <c r="F75">
+        <v>106.507</v>
+      </c>
+      <c r="G75">
+        <v>1.42</v>
+      </c>
+      <c r="H75">
+        <v>141.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1.72</v>
+      </c>
+      <c r="K75">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L75">
+        <v>1.65</v>
+      </c>
+      <c r="M75">
+        <v>25.4338716</v>
+      </c>
+      <c r="N75">
+        <v>-23.7838716</v>
+      </c>
+      <c r="O75">
+        <v>-5.470290467999999</v>
+      </c>
+      <c r="P75">
+        <v>-18.313581132</v>
+      </c>
+      <c r="Q75">
+        <v>-18.243581132</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.356943143630273</v>
+      </c>
+      <c r="T75">
+        <v>1.856978903441045</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.01492104725416637</v>
+      </c>
+      <c r="W75">
+        <v>0.2352368539157051</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.06487411849637548</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2700975521386385</v>
+      </c>
+      <c r="C76">
+        <v>-51.39684110476332</v>
+      </c>
+      <c r="D76">
+        <v>55.14915889523666</v>
+      </c>
+      <c r="E76">
+        <v>103.266</v>
+      </c>
+      <c r="F76">
+        <v>107.966</v>
+      </c>
+      <c r="G76">
+        <v>1.42</v>
+      </c>
+      <c r="H76">
+        <v>141.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1.72</v>
+      </c>
+      <c r="K76">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L76">
+        <v>1.65</v>
+      </c>
+      <c r="M76">
+        <v>25.7822808</v>
+      </c>
+      <c r="N76">
+        <v>-24.1322808</v>
+      </c>
+      <c r="O76">
+        <v>-5.550424583999999</v>
+      </c>
+      <c r="P76">
+        <v>-18.581856216</v>
+      </c>
+      <c r="Q76">
+        <v>-18.511856216</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3691794183852836</v>
+      </c>
+      <c r="T76">
+        <v>1.928401168958009</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.01471941148046142</v>
+      </c>
+      <c r="W76">
+        <v>0.2352850045384658</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.06399744121939743</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2720975521386385</v>
+      </c>
+      <c r="C77">
+        <v>-53.32862068079987</v>
+      </c>
+      <c r="D77">
+        <v>54.67637931920011</v>
+      </c>
+      <c r="E77">
+        <v>104.725</v>
+      </c>
+      <c r="F77">
+        <v>109.425</v>
+      </c>
+      <c r="G77">
+        <v>1.42</v>
+      </c>
+      <c r="H77">
+        <v>141.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1.72</v>
+      </c>
+      <c r="K77">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L77">
+        <v>1.65</v>
+      </c>
+      <c r="M77">
+        <v>26.13069</v>
+      </c>
+      <c r="N77">
+        <v>-24.48069</v>
+      </c>
+      <c r="O77">
+        <v>-5.630558699999999</v>
+      </c>
+      <c r="P77">
+        <v>-18.8501313</v>
+      </c>
+      <c r="Q77">
+        <v>-18.7801313</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3823945951206949</v>
+      </c>
+      <c r="T77">
+        <v>2.005537215716329</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.01452315266072193</v>
+      </c>
+      <c r="W77">
+        <v>0.2353318711446196</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.06314414200313878</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2740975521386384</v>
+      </c>
+      <c r="C78">
+        <v>-55.25236312135857</v>
+      </c>
+      <c r="D78">
+        <v>54.21163687864141</v>
+      </c>
+      <c r="E78">
+        <v>106.184</v>
+      </c>
+      <c r="F78">
+        <v>110.884</v>
+      </c>
+      <c r="G78">
+        <v>1.42</v>
+      </c>
+      <c r="H78">
+        <v>141.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1.72</v>
+      </c>
+      <c r="K78">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L78">
+        <v>1.65</v>
+      </c>
+      <c r="M78">
+        <v>26.4790992</v>
+      </c>
+      <c r="N78">
+        <v>-24.8290992</v>
+      </c>
+      <c r="O78">
+        <v>-5.710692815999999</v>
+      </c>
+      <c r="P78">
+        <v>-19.118406384</v>
+      </c>
+      <c r="Q78">
+        <v>-19.048406384</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3967110365840573</v>
+      </c>
+      <c r="T78">
+        <v>2.089101266371177</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.01433205854676506</v>
+      </c>
+      <c r="W78">
+        <v>0.2353775044190325</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.06231329802941332</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2760975521386385</v>
+      </c>
+      <c r="C79">
+        <v>-57.16827164308636</v>
+      </c>
+      <c r="D79">
+        <v>53.75472835691363</v>
+      </c>
+      <c r="E79">
+        <v>107.643</v>
+      </c>
+      <c r="F79">
+        <v>112.343</v>
+      </c>
+      <c r="G79">
+        <v>1.42</v>
+      </c>
+      <c r="H79">
+        <v>141.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1.72</v>
+      </c>
+      <c r="K79">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L79">
+        <v>1.65</v>
+      </c>
+      <c r="M79">
+        <v>26.8275084</v>
+      </c>
+      <c r="N79">
+        <v>-25.1775084</v>
+      </c>
+      <c r="O79">
+        <v>-5.790826932</v>
+      </c>
+      <c r="P79">
+        <v>-19.386681468</v>
+      </c>
+      <c r="Q79">
+        <v>-19.316681468</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4122723860007554</v>
+      </c>
+      <c r="T79">
+        <v>2.179931756213402</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.0141459279162876</v>
+      </c>
+      <c r="W79">
+        <v>0.2354219524135905</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.06150403441864172</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2780975521386385</v>
+      </c>
+      <c r="C80">
+        <v>-59.07654266885741</v>
+      </c>
+      <c r="D80">
+        <v>53.30545733114258</v>
+      </c>
+      <c r="E80">
+        <v>109.102</v>
+      </c>
+      <c r="F80">
+        <v>113.802</v>
+      </c>
+      <c r="G80">
+        <v>1.42</v>
+      </c>
+      <c r="H80">
+        <v>141.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1.72</v>
+      </c>
+      <c r="K80">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L80">
+        <v>1.65</v>
+      </c>
+      <c r="M80">
+        <v>27.1759176</v>
+      </c>
+      <c r="N80">
+        <v>-25.5259176</v>
+      </c>
+      <c r="O80">
+        <v>-5.870961048</v>
+      </c>
+      <c r="P80">
+        <v>-19.654956552</v>
+      </c>
+      <c r="Q80">
+        <v>-19.584956552</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4292484035462443</v>
+      </c>
+      <c r="T80">
+        <v>2.279019563314011</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.01396456986607878</v>
+      </c>
+      <c r="W80">
+        <v>0.2354652607159804</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.06071552115686418</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2800975521386385</v>
+      </c>
+      <c r="C81">
+        <v>-60.97736610932493</v>
+      </c>
+      <c r="D81">
+        <v>52.86363389067505</v>
+      </c>
+      <c r="E81">
+        <v>110.561</v>
+      </c>
+      <c r="F81">
+        <v>115.261</v>
+      </c>
+      <c r="G81">
+        <v>1.42</v>
+      </c>
+      <c r="H81">
+        <v>141.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1.72</v>
+      </c>
+      <c r="K81">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L81">
+        <v>1.65</v>
+      </c>
+      <c r="M81">
+        <v>27.5243268</v>
+      </c>
+      <c r="N81">
+        <v>-25.8743268</v>
+      </c>
+      <c r="O81">
+        <v>-5.951095163999999</v>
+      </c>
+      <c r="P81">
+        <v>-19.923231636</v>
+      </c>
+      <c r="Q81">
+        <v>-19.853231636</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.447841184667494</v>
+      </c>
+      <c r="T81">
+        <v>2.387544304424202</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.01378780315891323</v>
+      </c>
+      <c r="W81">
+        <v>0.2355074726056515</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.05994697025614437</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2820975521386385</v>
+      </c>
+      <c r="C82">
+        <v>-62.87092563058597</v>
+      </c>
+      <c r="D82">
+        <v>52.42907436941402</v>
+      </c>
+      <c r="E82">
+        <v>112.02</v>
+      </c>
+      <c r="F82">
+        <v>116.72</v>
+      </c>
+      <c r="G82">
+        <v>1.42</v>
+      </c>
+      <c r="H82">
+        <v>141.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1.72</v>
+      </c>
+      <c r="K82">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L82">
+        <v>1.65</v>
+      </c>
+      <c r="M82">
+        <v>27.872736</v>
+      </c>
+      <c r="N82">
+        <v>-26.222736</v>
+      </c>
+      <c r="O82">
+        <v>-6.031229279999999</v>
+      </c>
+      <c r="P82">
+        <v>-20.19150672</v>
+      </c>
+      <c r="Q82">
+        <v>-20.12150672</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4682932439008687</v>
+      </c>
+      <c r="T82">
+        <v>2.506921519645412</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.01361545561942681</v>
+      </c>
+      <c r="W82">
+        <v>0.2355486291980809</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.05919763312794257</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2840975521386385</v>
+      </c>
+      <c r="C83">
+        <v>-64.75739890875209</v>
+      </c>
+      <c r="D83">
+        <v>52.0016010912479</v>
+      </c>
+      <c r="E83">
+        <v>113.479</v>
+      </c>
+      <c r="F83">
+        <v>118.179</v>
+      </c>
+      <c r="G83">
+        <v>1.42</v>
+      </c>
+      <c r="H83">
+        <v>141.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1.72</v>
+      </c>
+      <c r="K83">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L83">
+        <v>1.65</v>
+      </c>
+      <c r="M83">
+        <v>28.2211452</v>
+      </c>
+      <c r="N83">
+        <v>-26.5711452</v>
+      </c>
+      <c r="O83">
+        <v>-6.111363396</v>
+      </c>
+      <c r="P83">
+        <v>-20.459781804</v>
+      </c>
+      <c r="Q83">
+        <v>-20.389781804</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4908981514745988</v>
+      </c>
+      <c r="T83">
+        <v>2.638864757521487</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.01344736357474253</v>
+      </c>
+      <c r="W83">
+        <v>0.2355887695783515</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.05846679815105438</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2860975521386384</v>
+      </c>
+      <c r="C84">
+        <v>-66.6369578721671</v>
+      </c>
+      <c r="D84">
+        <v>51.58104212783289</v>
+      </c>
+      <c r="E84">
+        <v>114.938</v>
+      </c>
+      <c r="F84">
+        <v>119.638</v>
+      </c>
+      <c r="G84">
+        <v>1.42</v>
+      </c>
+      <c r="H84">
+        <v>141.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1.72</v>
+      </c>
+      <c r="K84">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L84">
+        <v>1.65</v>
+      </c>
+      <c r="M84">
+        <v>28.5695544</v>
+      </c>
+      <c r="N84">
+        <v>-26.9195544</v>
+      </c>
+      <c r="O84">
+        <v>-6.191497512</v>
+      </c>
+      <c r="P84">
+        <v>-20.728056888</v>
+      </c>
+      <c r="Q84">
+        <v>-20.658056888</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5160147154454097</v>
+      </c>
+      <c r="T84">
+        <v>2.785468355161569</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.01328337133602616</v>
+      </c>
+      <c r="W84">
+        <v>0.235627930924957</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.057753788417505</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2880975521386384</v>
+      </c>
+      <c r="C85">
+        <v>-68.50976893196562</v>
+      </c>
+      <c r="D85">
+        <v>51.16723106803438</v>
+      </c>
+      <c r="E85">
+        <v>116.397</v>
+      </c>
+      <c r="F85">
+        <v>121.097</v>
+      </c>
+      <c r="G85">
+        <v>1.42</v>
+      </c>
+      <c r="H85">
+        <v>141.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1.72</v>
+      </c>
+      <c r="K85">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L85">
+        <v>1.65</v>
+      </c>
+      <c r="M85">
+        <v>28.9179636</v>
+      </c>
+      <c r="N85">
+        <v>-27.2679636</v>
+      </c>
+      <c r="O85">
+        <v>-6.271631628</v>
+      </c>
+      <c r="P85">
+        <v>-20.996331972</v>
+      </c>
+      <c r="Q85">
+        <v>-20.926331972</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5440861692951398</v>
+      </c>
+      <c r="T85">
+        <v>2.949319434876956</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.01312333071751982</v>
+      </c>
+      <c r="W85">
+        <v>0.2356661486246563</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.05705795964139049</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2900975521386384</v>
+      </c>
+      <c r="C86">
+        <v>-70.37599320162188</v>
+      </c>
+      <c r="D86">
+        <v>50.7600067983781</v>
+      </c>
+      <c r="E86">
+        <v>117.856</v>
+      </c>
+      <c r="F86">
+        <v>122.556</v>
+      </c>
+      <c r="G86">
+        <v>1.42</v>
+      </c>
+      <c r="H86">
+        <v>141.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1.72</v>
+      </c>
+      <c r="K86">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L86">
+        <v>1.65</v>
+      </c>
+      <c r="M86">
+        <v>29.2663728</v>
+      </c>
+      <c r="N86">
+        <v>-27.6163728</v>
+      </c>
+      <c r="O86">
+        <v>-6.351765744</v>
+      </c>
+      <c r="P86">
+        <v>-21.264607056</v>
+      </c>
+      <c r="Q86">
+        <v>-21.194607056</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5756665548760858</v>
+      </c>
+      <c r="T86">
+        <v>3.133651899556764</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.0129671005899303</v>
+      </c>
+      <c r="W86">
+        <v>0.2357034563791247</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.05637869821708819</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2920975521386384</v>
+      </c>
+      <c r="C87">
+        <v>-72.23578670609756</v>
+      </c>
+      <c r="D87">
+        <v>50.35921329390241</v>
+      </c>
+      <c r="E87">
+        <v>119.315</v>
+      </c>
+      <c r="F87">
+        <v>124.015</v>
+      </c>
+      <c r="G87">
+        <v>1.42</v>
+      </c>
+      <c r="H87">
+        <v>141.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1.72</v>
+      </c>
+      <c r="K87">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L87">
+        <v>1.65</v>
+      </c>
+      <c r="M87">
+        <v>29.61478199999999</v>
+      </c>
+      <c r="N87">
+        <v>-27.964782</v>
+      </c>
+      <c r="O87">
+        <v>-6.431899859999999</v>
+      </c>
+      <c r="P87">
+        <v>-21.53288214</v>
+      </c>
+      <c r="Q87">
+        <v>-21.46288214</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.6114576585344915</v>
+      </c>
+      <c r="T87">
+        <v>3.342562026193882</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.01281454646534288</v>
+      </c>
+      <c r="W87">
+        <v>0.2357398863040761</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.05571541941453428</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2940975521386385</v>
+      </c>
+      <c r="C88">
+        <v>-74.08930058115857</v>
+      </c>
+      <c r="D88">
+        <v>49.9646994188414</v>
+      </c>
+      <c r="E88">
+        <v>120.774</v>
+      </c>
+      <c r="F88">
+        <v>125.474</v>
+      </c>
+      <c r="G88">
+        <v>1.42</v>
+      </c>
+      <c r="H88">
+        <v>141.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1.72</v>
+      </c>
+      <c r="K88">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L88">
+        <v>1.65</v>
+      </c>
+      <c r="M88">
+        <v>29.9631912</v>
+      </c>
+      <c r="N88">
+        <v>-28.3131912</v>
+      </c>
+      <c r="O88">
+        <v>-6.512033975999999</v>
+      </c>
+      <c r="P88">
+        <v>-21.801157224</v>
+      </c>
+      <c r="Q88">
+        <v>-21.731157224</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6523617770012409</v>
+      </c>
+      <c r="T88">
+        <v>3.581316456636302</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.01266554011109471</v>
+      </c>
+      <c r="W88">
+        <v>0.2357754690214706</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.05506756570041171</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2960975521386385</v>
+      </c>
+      <c r="C89">
+        <v>-75.93668126339625</v>
+      </c>
+      <c r="D89">
+        <v>49.57631873660373</v>
+      </c>
+      <c r="E89">
+        <v>122.233</v>
+      </c>
+      <c r="F89">
+        <v>126.933</v>
+      </c>
+      <c r="G89">
+        <v>1.42</v>
+      </c>
+      <c r="H89">
+        <v>141.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1.72</v>
+      </c>
+      <c r="K89">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L89">
+        <v>1.65</v>
+      </c>
+      <c r="M89">
+        <v>30.3116004</v>
+      </c>
+      <c r="N89">
+        <v>-28.6616004</v>
+      </c>
+      <c r="O89">
+        <v>-6.592168091999999</v>
+      </c>
+      <c r="P89">
+        <v>-22.069432308</v>
+      </c>
+      <c r="Q89">
+        <v>-21.999432308</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6995588367705672</v>
+      </c>
+      <c r="T89">
+        <v>3.856802337916017</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.01251995919027753</v>
+      </c>
+      <c r="W89">
+        <v>0.2358102337453618</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.05443460517511967</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2980975521386384</v>
+      </c>
+      <c r="C90">
+        <v>-77.77807067145432</v>
+      </c>
+      <c r="D90">
+        <v>49.19392932854564</v>
+      </c>
+      <c r="E90">
+        <v>123.692</v>
+      </c>
+      <c r="F90">
+        <v>128.392</v>
+      </c>
+      <c r="G90">
+        <v>1.42</v>
+      </c>
+      <c r="H90">
+        <v>141.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1.72</v>
+      </c>
+      <c r="K90">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L90">
+        <v>1.65</v>
+      </c>
+      <c r="M90">
+        <v>30.6600096</v>
+      </c>
+      <c r="N90">
+        <v>-29.0100096</v>
+      </c>
+      <c r="O90">
+        <v>-6.672302207999999</v>
+      </c>
+      <c r="P90">
+        <v>-22.337707392</v>
+      </c>
+      <c r="Q90">
+        <v>-22.267707392</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7546220731681146</v>
+      </c>
+      <c r="T90">
+        <v>4.178202532742353</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.01237768692675165</v>
+      </c>
+      <c r="W90">
+        <v>0.2358442083618917</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.05381603011631142</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3000975521386384</v>
+      </c>
+      <c r="C91">
+        <v>-79.61360637893347</v>
+      </c>
+      <c r="D91">
+        <v>48.81739362106649</v>
+      </c>
+      <c r="E91">
+        <v>125.151</v>
+      </c>
+      <c r="F91">
+        <v>129.851</v>
+      </c>
+      <c r="G91">
+        <v>1.42</v>
+      </c>
+      <c r="H91">
+        <v>141.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1.72</v>
+      </c>
+      <c r="K91">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L91">
+        <v>1.65</v>
+      </c>
+      <c r="M91">
+        <v>31.00841879999999</v>
+      </c>
+      <c r="N91">
+        <v>-29.3584188</v>
+      </c>
+      <c r="O91">
+        <v>-6.752436323999999</v>
+      </c>
+      <c r="P91">
+        <v>-22.605982476</v>
+      </c>
+      <c r="Q91">
+        <v>-22.535982476</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.8196968070924886</v>
+      </c>
+      <c r="T91">
+        <v>4.558039126628022</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.0122386117927432</v>
+      </c>
+      <c r="W91">
+        <v>0.2358774195038929</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.05321135562062262</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3020975521386384</v>
+      </c>
+      <c r="C92">
+        <v>-81.44342177941513</v>
+      </c>
+      <c r="D92">
+        <v>48.44657822058484</v>
+      </c>
+      <c r="E92">
+        <v>126.61</v>
+      </c>
+      <c r="F92">
+        <v>131.31</v>
+      </c>
+      <c r="G92">
+        <v>1.42</v>
+      </c>
+      <c r="H92">
+        <v>141.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1.72</v>
+      </c>
+      <c r="K92">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L92">
+        <v>1.65</v>
+      </c>
+      <c r="M92">
+        <v>31.356828</v>
+      </c>
+      <c r="N92">
+        <v>-29.706828</v>
+      </c>
+      <c r="O92">
+        <v>-6.832570439999999</v>
+      </c>
+      <c r="P92">
+        <v>-22.87425756</v>
+      </c>
+      <c r="Q92">
+        <v>-22.80425756</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8977864878017374</v>
+      </c>
+      <c r="T92">
+        <v>5.013843039290824</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.01210262721726828</v>
+      </c>
+      <c r="W92">
+        <v>0.2359098926205163</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.05262011833594904</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3040975521386384</v>
+      </c>
+      <c r="C93">
+        <v>-83.26764624402135</v>
+      </c>
+      <c r="D93">
+        <v>48.08135375597863</v>
+      </c>
+      <c r="E93">
+        <v>128.069</v>
+      </c>
+      <c r="F93">
+        <v>132.769</v>
+      </c>
+      <c r="G93">
+        <v>1.42</v>
+      </c>
+      <c r="H93">
+        <v>141.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1.72</v>
+      </c>
+      <c r="K93">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L93">
+        <v>1.65</v>
+      </c>
+      <c r="M93">
+        <v>31.7052372</v>
+      </c>
+      <c r="N93">
+        <v>-30.0552372</v>
+      </c>
+      <c r="O93">
+        <v>-6.912704555999999</v>
+      </c>
+      <c r="P93">
+        <v>-23.142532644</v>
+      </c>
+      <c r="Q93">
+        <v>-23.072532644</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.9932294308908194</v>
+      </c>
+      <c r="T93">
+        <v>5.570936710323138</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.01196963131378181</v>
+      </c>
+      <c r="W93">
+        <v>0.2359416520422689</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.05204187527731219</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3060975521386384</v>
+      </c>
+      <c r="C94">
+        <v>-85.08640527190082</v>
+      </c>
+      <c r="D94">
+        <v>47.72159472809917</v>
+      </c>
+      <c r="E94">
+        <v>129.528</v>
+      </c>
+      <c r="F94">
+        <v>134.228</v>
+      </c>
+      <c r="G94">
+        <v>1.42</v>
+      </c>
+      <c r="H94">
+        <v>141.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1.72</v>
+      </c>
+      <c r="K94">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L94">
+        <v>1.65</v>
+      </c>
+      <c r="M94">
+        <v>32.0536464</v>
+      </c>
+      <c r="N94">
+        <v>-30.4036464</v>
+      </c>
+      <c r="O94">
+        <v>-6.992838672</v>
+      </c>
+      <c r="P94">
+        <v>-23.410807728</v>
+      </c>
+      <c r="Q94">
+        <v>-23.340807728</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.112533109752172</v>
+      </c>
+      <c r="T94">
+        <v>6.267303799113532</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.01183952662558853</v>
+      </c>
+      <c r="W94">
+        <v>0.2359727210418095</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.05147620271995013</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3080975521386384</v>
+      </c>
+      <c r="C95">
+        <v>-86.8998206340095</v>
+      </c>
+      <c r="D95">
+        <v>47.36717936599048</v>
+      </c>
+      <c r="E95">
+        <v>130.987</v>
+      </c>
+      <c r="F95">
+        <v>135.687</v>
+      </c>
+      <c r="G95">
+        <v>1.42</v>
+      </c>
+      <c r="H95">
+        <v>141.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1.72</v>
+      </c>
+      <c r="K95">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L95">
+        <v>1.65</v>
+      </c>
+      <c r="M95">
+        <v>32.4020556</v>
+      </c>
+      <c r="N95">
+        <v>-30.7520556</v>
+      </c>
+      <c r="O95">
+        <v>-7.072972788</v>
+      </c>
+      <c r="P95">
+        <v>-23.679082812</v>
+      </c>
+      <c r="Q95">
+        <v>-23.609082812</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.265923554002482</v>
+      </c>
+      <c r="T95">
+        <v>7.162632913272609</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.01171221988767898</v>
+      </c>
+      <c r="W95">
+        <v>0.2360031218908223</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.05092269516382164</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3100975521386384</v>
+      </c>
+      <c r="C96">
+        <v>-88.70801051053139</v>
+      </c>
+      <c r="D96">
+        <v>47.01798948946859</v>
+      </c>
+      <c r="E96">
+        <v>132.446</v>
+      </c>
+      <c r="F96">
+        <v>137.146</v>
+      </c>
+      <c r="G96">
+        <v>1.42</v>
+      </c>
+      <c r="H96">
+        <v>141.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1.72</v>
+      </c>
+      <c r="K96">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L96">
+        <v>1.65</v>
+      </c>
+      <c r="M96">
+        <v>32.7504648</v>
+      </c>
+      <c r="N96">
+        <v>-31.1004648</v>
+      </c>
+      <c r="O96">
+        <v>-7.153106903999999</v>
+      </c>
+      <c r="P96">
+        <v>-23.947357896</v>
+      </c>
+      <c r="Q96">
+        <v>-23.877357896</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.47044414633623</v>
+      </c>
+      <c r="T96">
+        <v>8.356405065484713</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.0115876218037675</v>
+      </c>
+      <c r="W96">
+        <v>0.2360328759132603</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.05038096436420647</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3120975521386385</v>
+      </c>
+      <c r="C97">
+        <v>-90.51108962226539</v>
+      </c>
+      <c r="D97">
+        <v>46.67391037773459</v>
+      </c>
+      <c r="E97">
+        <v>133.905</v>
+      </c>
+      <c r="F97">
+        <v>138.605</v>
+      </c>
+      <c r="G97">
+        <v>1.42</v>
+      </c>
+      <c r="H97">
+        <v>141.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1.72</v>
+      </c>
+      <c r="K97">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L97">
+        <v>1.65</v>
+      </c>
+      <c r="M97">
+        <v>33.098874</v>
+      </c>
+      <c r="N97">
+        <v>-31.448874</v>
+      </c>
+      <c r="O97">
+        <v>-7.23324102</v>
+      </c>
+      <c r="P97">
+        <v>-24.21563298</v>
+      </c>
+      <c r="Q97">
+        <v>-24.14563298</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.756772975603477</v>
+      </c>
+      <c r="T97">
+        <v>10.02768607858166</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.01146564683741205</v>
+      </c>
+      <c r="W97">
+        <v>0.236062003535226</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.04985063842353066</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3140975521386384</v>
+      </c>
+      <c r="C98">
+        <v>-92.30916935628515</v>
+      </c>
+      <c r="D98">
+        <v>46.33483064371481</v>
+      </c>
+      <c r="E98">
+        <v>135.364</v>
+      </c>
+      <c r="F98">
+        <v>140.064</v>
+      </c>
+      <c r="G98">
+        <v>1.42</v>
+      </c>
+      <c r="H98">
+        <v>141.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1.72</v>
+      </c>
+      <c r="K98">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L98">
+        <v>1.65</v>
+      </c>
+      <c r="M98">
+        <v>33.44728319999999</v>
+      </c>
+      <c r="N98">
+        <v>-31.7972832</v>
+      </c>
+      <c r="O98">
+        <v>-7.313375135999999</v>
+      </c>
+      <c r="P98">
+        <v>-24.483908064</v>
+      </c>
+      <c r="Q98">
+        <v>-24.413908064</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.186266219504342</v>
+      </c>
+      <c r="T98">
+        <v>12.53460759822705</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01134621301618901</v>
+      </c>
+      <c r="W98">
+        <v>0.2360905243317341</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.04933136093995216</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3160975521386384</v>
+      </c>
+      <c r="C99">
+        <v>-94.10235788616117</v>
+      </c>
+      <c r="D99">
+        <v>46.0006421138388</v>
+      </c>
+      <c r="E99">
+        <v>136.823</v>
+      </c>
+      <c r="F99">
+        <v>141.523</v>
+      </c>
+      <c r="G99">
+        <v>1.42</v>
+      </c>
+      <c r="H99">
+        <v>141.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1.72</v>
+      </c>
+      <c r="K99">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L99">
+        <v>1.65</v>
+      </c>
+      <c r="M99">
+        <v>33.79569239999999</v>
+      </c>
+      <c r="N99">
+        <v>-32.14569239999999</v>
+      </c>
+      <c r="O99">
+        <v>-7.393509251999999</v>
+      </c>
+      <c r="P99">
+        <v>-24.752183148</v>
+      </c>
+      <c r="Q99">
+        <v>-24.682183148</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.902088292672456</v>
+      </c>
+      <c r="T99">
+        <v>16.7128101309694</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.01122924174798088</v>
+      </c>
+      <c r="W99">
+        <v>0.2361184570705822</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.04882279020861247</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3180975521386384</v>
+      </c>
+      <c r="C100">
+        <v>-95.8907602870172</v>
+      </c>
+      <c r="D100">
+        <v>45.67123971298277</v>
+      </c>
+      <c r="E100">
+        <v>138.282</v>
+      </c>
+      <c r="F100">
+        <v>142.982</v>
+      </c>
+      <c r="G100">
+        <v>1.42</v>
+      </c>
+      <c r="H100">
+        <v>141.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1.72</v>
+      </c>
+      <c r="K100">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L100">
+        <v>1.65</v>
+      </c>
+      <c r="M100">
+        <v>34.14410159999999</v>
+      </c>
+      <c r="N100">
+        <v>-32.49410159999999</v>
+      </c>
+      <c r="O100">
+        <v>-7.473643367999998</v>
+      </c>
+      <c r="P100">
+        <v>-25.020458232</v>
+      </c>
+      <c r="Q100">
+        <v>-24.950458232</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.333732439008682</v>
+      </c>
+      <c r="T100">
+        <v>25.06921519645409</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.01111465764851169</v>
+      </c>
+      <c r="W100">
+        <v>0.2361458197535354</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.04832459847178994</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3200975521386384</v>
+      </c>
+      <c r="C101">
+        <v>-97.67447864567873</v>
+      </c>
+      <c r="D101">
+        <v>45.34652135432123</v>
+      </c>
+      <c r="E101">
+        <v>139.741</v>
+      </c>
+      <c r="F101">
+        <v>144.441</v>
+      </c>
+      <c r="G101">
+        <v>1.42</v>
+      </c>
+      <c r="H101">
+        <v>141.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1.72</v>
+      </c>
+      <c r="K101">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="L101">
+        <v>1.65</v>
+      </c>
+      <c r="M101">
+        <v>34.4925108</v>
+      </c>
+      <c r="N101">
+        <v>-32.8425108</v>
+      </c>
+      <c r="O101">
+        <v>-7.553777483999999</v>
+      </c>
+      <c r="P101">
+        <v>-25.288733316</v>
+      </c>
+      <c r="Q101">
+        <v>-25.218733316</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>8.628664878017366</v>
+      </c>
+      <c r="T101">
+        <v>50.13843039290819</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.0110023883793348</v>
+      </c>
+      <c r="W101">
+        <v>0.2361726296550149</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.04783647121449908</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
